--- a/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_CropCanopy.xlsx
+++ b/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_CropCanopy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kelly.thorp\Documents\cottondata\Data\2023_F013B4_CO_TILL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2023_F013B4_CO_TILL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E024AF-F878-4489-B4D6-2E772C2B2075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728C4A64-2481-4704-818E-0E408A03FFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="495" windowWidth="15165" windowHeight="14970" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16455" yWindow="-28440" windowWidth="17805" windowHeight="11445" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="12" r:id="rId1"/>
@@ -3044,60 +3044,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="19" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3132,12 +3078,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3151,6 +3091,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="19" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -11283,10 +11283,10 @@
       <c r="H3" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="203" t="s">
+      <c r="I3" s="221" t="s">
         <v>421</v>
       </c>
-      <c r="J3" s="204"/>
+      <c r="J3" s="222"/>
       <c r="K3" s="118"/>
       <c r="L3" s="120" t="s">
         <v>223</v>
@@ -11296,24 +11296,24 @@
       <c r="H4" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="205"/>
-      <c r="J4" s="206"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="224"/>
       <c r="K4" s="118"/>
     </row>
     <row r="5" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="207" t="s">
+      <c r="B5" s="225" t="s">
         <v>420</v>
       </c>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
       <c r="M5" s="117"/>
     </row>
     <row r="6" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -17651,33 +17651,33 @@
       <c r="C11" s="186" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="214">
+      <c r="D11" s="227">
         <v>45048</v>
       </c>
-      <c r="E11" s="216"/>
-      <c r="F11" s="214">
+      <c r="E11" s="228"/>
+      <c r="F11" s="227">
         <v>45050</v>
       </c>
-      <c r="G11" s="216"/>
-      <c r="H11" s="214">
+      <c r="G11" s="228"/>
+      <c r="H11" s="227">
         <v>45054</v>
       </c>
-      <c r="I11" s="216"/>
-      <c r="J11" s="214">
+      <c r="I11" s="228"/>
+      <c r="J11" s="227">
         <v>45057</v>
       </c>
-      <c r="K11" s="215"/>
-      <c r="L11" s="216"/>
-      <c r="M11" s="214">
+      <c r="K11" s="236"/>
+      <c r="L11" s="228"/>
+      <c r="M11" s="227">
         <v>45061</v>
       </c>
-      <c r="N11" s="215"/>
-      <c r="O11" s="216"/>
-      <c r="P11" s="214">
+      <c r="N11" s="236"/>
+      <c r="O11" s="228"/>
+      <c r="P11" s="227">
         <v>45064</v>
       </c>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="216"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="228"/>
     </row>
     <row r="12" spans="1:18" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="184" t="s">
@@ -17686,33 +17686,33 @@
       <c r="C12" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="217">
+      <c r="D12" s="229">
         <v>122</v>
       </c>
-      <c r="E12" s="211"/>
-      <c r="F12" s="217">
+      <c r="E12" s="230"/>
+      <c r="F12" s="229">
         <v>124</v>
       </c>
-      <c r="G12" s="211"/>
-      <c r="H12" s="217">
+      <c r="G12" s="230"/>
+      <c r="H12" s="229">
         <v>128</v>
       </c>
-      <c r="I12" s="211"/>
-      <c r="J12" s="217">
+      <c r="I12" s="230"/>
+      <c r="J12" s="229">
         <v>131</v>
       </c>
-      <c r="K12" s="218"/>
-      <c r="L12" s="211"/>
-      <c r="M12" s="217">
+      <c r="K12" s="237"/>
+      <c r="L12" s="230"/>
+      <c r="M12" s="229">
         <v>135</v>
       </c>
-      <c r="N12" s="218"/>
-      <c r="O12" s="211"/>
-      <c r="P12" s="217">
+      <c r="N12" s="237"/>
+      <c r="O12" s="230"/>
+      <c r="P12" s="229">
         <v>138</v>
       </c>
-      <c r="Q12" s="218"/>
-      <c r="R12" s="211"/>
+      <c r="Q12" s="237"/>
+      <c r="R12" s="230"/>
     </row>
     <row r="13" spans="1:18" s="178" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="181" t="s">
@@ -17721,50 +17721,50 @@
       <c r="C13" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="209" t="s">
+      <c r="D13" s="233" t="s">
         <v>458</v>
       </c>
-      <c r="E13" s="211"/>
-      <c r="F13" s="209" t="s">
+      <c r="E13" s="230"/>
+      <c r="F13" s="233" t="s">
         <v>457</v>
       </c>
-      <c r="G13" s="211"/>
-      <c r="H13" s="209" t="s">
+      <c r="G13" s="230"/>
+      <c r="H13" s="233" t="s">
         <v>456</v>
       </c>
-      <c r="I13" s="211"/>
-      <c r="J13" s="209" t="s">
+      <c r="I13" s="230"/>
+      <c r="J13" s="233" t="s">
         <v>455</v>
       </c>
-      <c r="K13" s="210"/>
-      <c r="L13" s="211"/>
-      <c r="M13" s="209" t="s">
+      <c r="K13" s="235"/>
+      <c r="L13" s="230"/>
+      <c r="M13" s="233" t="s">
         <v>454</v>
       </c>
-      <c r="N13" s="210"/>
-      <c r="O13" s="211"/>
-      <c r="P13" s="209" t="s">
+      <c r="N13" s="235"/>
+      <c r="O13" s="230"/>
+      <c r="P13" s="233" t="s">
         <v>453</v>
       </c>
-      <c r="Q13" s="210"/>
-      <c r="R13" s="211"/>
+      <c r="Q13" s="235"/>
+      <c r="R13" s="230"/>
     </row>
     <row r="14" spans="1:18" s="131" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="174"/>
       <c r="B14" s="173"/>
       <c r="C14" s="172"/>
-      <c r="D14" s="219"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="212"/>
-      <c r="G14" s="213"/>
-      <c r="H14" s="212"/>
-      <c r="I14" s="213"/>
-      <c r="J14" s="212"/>
-      <c r="K14" s="212"/>
-      <c r="L14" s="213"/>
-      <c r="M14" s="212"/>
-      <c r="N14" s="212"/>
-      <c r="O14" s="213"/>
+      <c r="D14" s="231"/>
+      <c r="E14" s="232"/>
+      <c r="F14" s="234"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="234"/>
+      <c r="I14" s="232"/>
+      <c r="J14" s="234"/>
+      <c r="K14" s="234"/>
+      <c r="L14" s="232"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="234"/>
+      <c r="O14" s="232"/>
       <c r="P14" s="176"/>
       <c r="Q14" s="176"/>
       <c r="R14" s="175"/>
@@ -27011,18 +27011,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="J14:L14"/>
@@ -27034,6 +27022,18 @@
     <mergeCell ref="P13:R13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0.25"/>
@@ -27131,7 +27131,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="130">
-        <f t="shared" ref="I3:I34" si="0">H3/2</f>
+        <f>H3/2</f>
         <v>4.5</v>
       </c>
       <c r="J3" s="134">
@@ -27179,7 +27179,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="130">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I3:I34" si="0">H4/2</f>
         <v>4</v>
       </c>
       <c r="J4" s="134">
@@ -34323,7 +34323,7 @@
         <v>7</v>
       </c>
       <c r="I163" s="130">
-        <f t="shared" ref="I163:I194" si="17">H163/2</f>
+        <f t="shared" ref="I163:I182" si="17">H163/2</f>
         <v>3.5</v>
       </c>
       <c r="J163" s="134">
@@ -34340,7 +34340,7 @@
         <v>5</v>
       </c>
       <c r="O163" s="134">
-        <f t="shared" ref="O163:O194" si="18">M$2+(I163-M163)/(N163-M163)*(N$2-M$2)</f>
+        <f t="shared" ref="O163:O182" si="18">M$2+(I163-M163)/(N163-M163)*(N$2-M$2)</f>
         <v>136.875</v>
       </c>
     </row>
@@ -39163,18 +39163,18 @@
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B195" s="220" t="s">
+      <c r="B195" s="202" t="s">
         <v>477</v>
       </c>
-      <c r="C195" s="221">
+      <c r="C195" s="203">
         <f>AVERAGE(C12:C26)</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="D195" s="221">
+      <c r="D195" s="203">
         <f t="shared" ref="D195:E195" si="7">AVERAGE(D12:D26)</f>
         <v>6.4</v>
       </c>
-      <c r="E195" s="221">
+      <c r="E195" s="203">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
@@ -39184,18 +39184,18 @@
       </c>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B196" s="220" t="s">
+      <c r="B196" s="202" t="s">
         <v>478</v>
       </c>
-      <c r="C196" s="221">
+      <c r="C196" s="203">
         <f>AVERAGE(C27:C41)</f>
         <v>0.26666666666666666</v>
       </c>
-      <c r="D196" s="221">
+      <c r="D196" s="203">
         <f t="shared" ref="D196:E196" si="8">AVERAGE(D27:D41)</f>
         <v>5.666666666666667</v>
       </c>
-      <c r="E196" s="221">
+      <c r="E196" s="203">
         <f t="shared" si="8"/>
         <v>9.7333333333333325</v>
       </c>
@@ -39205,18 +39205,18 @@
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B197" s="220" t="s">
+      <c r="B197" s="202" t="s">
         <v>479</v>
       </c>
-      <c r="C197" s="221">
+      <c r="C197" s="203">
         <f>AVERAGE(C42:C56)</f>
         <v>0.2</v>
       </c>
-      <c r="D197" s="221">
+      <c r="D197" s="203">
         <f t="shared" ref="D197:E197" si="10">AVERAGE(D42:D56)</f>
         <v>5.9333333333333336</v>
       </c>
-      <c r="E197" s="221">
+      <c r="E197" s="203">
         <f t="shared" si="10"/>
         <v>9.8666666666666671</v>
       </c>
@@ -39226,18 +39226,18 @@
       </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B198" s="220" t="s">
+      <c r="B198" s="202" t="s">
         <v>480</v>
       </c>
-      <c r="C198" s="221">
+      <c r="C198" s="203">
         <f>AVERAGE(C57:C71)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="D198" s="221">
+      <c r="D198" s="203">
         <f t="shared" ref="D198:E198" si="11">AVERAGE(D57:D71)</f>
         <v>6.8666666666666663</v>
       </c>
-      <c r="E198" s="221">
+      <c r="E198" s="203">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
@@ -39247,18 +39247,18 @@
       </c>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B199" s="220" t="s">
+      <c r="B199" s="202" t="s">
         <v>481</v>
       </c>
-      <c r="C199" s="221">
+      <c r="C199" s="203">
         <f>AVERAGE(C72:C86)</f>
         <v>0.2</v>
       </c>
-      <c r="D199" s="221">
+      <c r="D199" s="203">
         <f t="shared" ref="D199:E199" si="12">AVERAGE(D72:D86)</f>
         <v>5.9333333333333336</v>
       </c>
-      <c r="E199" s="221">
+      <c r="E199" s="203">
         <f t="shared" si="12"/>
         <v>9.8000000000000007</v>
       </c>
@@ -39268,18 +39268,18 @@
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B200" s="220" t="s">
+      <c r="B200" s="202" t="s">
         <v>482</v>
       </c>
-      <c r="C200" s="221">
+      <c r="C200" s="203">
         <f>AVERAGE(C87:C101)</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="D200" s="221">
+      <c r="D200" s="203">
         <f t="shared" ref="D200:E200" si="13">AVERAGE(D87:D101)</f>
         <v>6.4</v>
       </c>
-      <c r="E200" s="221">
+      <c r="E200" s="203">
         <f t="shared" si="13"/>
         <v>9.8000000000000007</v>
       </c>
@@ -39289,18 +39289,18 @@
       </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B201" s="220" t="s">
+      <c r="B201" s="202" t="s">
         <v>483</v>
       </c>
-      <c r="C201" s="221">
+      <c r="C201" s="203">
         <f>AVERAGE(C102:C116)</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D201" s="221">
+      <c r="D201" s="203">
         <f t="shared" ref="D201:E201" si="14">AVERAGE(D102:D116)</f>
         <v>5.333333333333333</v>
       </c>
-      <c r="E201" s="221">
+      <c r="E201" s="203">
         <f t="shared" si="14"/>
         <v>9.4666666666666668</v>
       </c>
@@ -39310,18 +39310,18 @@
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B202" s="220" t="s">
+      <c r="B202" s="202" t="s">
         <v>484</v>
       </c>
-      <c r="C202" s="221">
+      <c r="C202" s="203">
         <f>AVERAGE(C117:C131)</f>
         <v>0.2</v>
       </c>
-      <c r="D202" s="221">
+      <c r="D202" s="203">
         <f t="shared" ref="D202:E202" si="15">AVERAGE(D117:D131)</f>
         <v>5.8</v>
       </c>
-      <c r="E202" s="221">
+      <c r="E202" s="203">
         <f t="shared" si="15"/>
         <v>9.7333333333333325</v>
       </c>
@@ -39331,18 +39331,18 @@
       </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B203" s="220" t="s">
+      <c r="B203" s="202" t="s">
         <v>485</v>
       </c>
-      <c r="C203" s="221">
+      <c r="C203" s="203">
         <f>AVERAGE(C132:C146)</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="D203" s="221">
+      <c r="D203" s="203">
         <f t="shared" ref="D203:E203" si="16">AVERAGE(D132:D146)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="E203" s="221">
+      <c r="E203" s="203">
         <f t="shared" si="16"/>
         <v>9.9333333333333336</v>
       </c>
@@ -39352,18 +39352,18 @@
       </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B204" s="220" t="s">
+      <c r="B204" s="202" t="s">
         <v>486</v>
       </c>
-      <c r="C204" s="221">
+      <c r="C204" s="203">
         <f>AVERAGE(C147:C161)</f>
         <v>0.26666666666666666</v>
       </c>
-      <c r="D204" s="221">
+      <c r="D204" s="203">
         <f t="shared" ref="D204:E204" si="17">AVERAGE(D147:D161)</f>
         <v>5.6</v>
       </c>
-      <c r="E204" s="221">
+      <c r="E204" s="203">
         <f t="shared" si="17"/>
         <v>9.7333333333333325</v>
       </c>
@@ -39373,18 +39373,18 @@
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B205" s="220" t="s">
+      <c r="B205" s="202" t="s">
         <v>487</v>
       </c>
-      <c r="C205" s="221">
+      <c r="C205" s="203">
         <f>AVERAGE(C162:C176)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="D205" s="221">
+      <c r="D205" s="203">
         <f t="shared" ref="D205:E205" si="18">AVERAGE(D162:D176)</f>
         <v>6.7333333333333334</v>
       </c>
-      <c r="E205" s="221">
+      <c r="E205" s="203">
         <f t="shared" si="18"/>
         <v>10</v>
       </c>
@@ -39394,18 +39394,18 @@
       </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B206" s="220" t="s">
+      <c r="B206" s="202" t="s">
         <v>488</v>
       </c>
-      <c r="C206" s="221">
+      <c r="C206" s="203">
         <f>AVERAGE(C177:C191)</f>
         <v>0.26666666666666666</v>
       </c>
-      <c r="D206" s="221">
+      <c r="D206" s="203">
         <f t="shared" ref="D206:E206" si="19">AVERAGE(D177:D191)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="E206" s="221">
+      <c r="E206" s="203">
         <f t="shared" si="19"/>
         <v>9.9333333333333336</v>
       </c>
@@ -39452,15 +39452,15 @@
       <c r="E1" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="F1" s="235">
+      <c r="F1" s="215">
         <v>45110</v>
       </c>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -39479,75 +39479,75 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>501</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="231" t="s">
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="231"/>
-      <c r="L4" s="231"/>
-      <c r="M4" s="230"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="212"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="228" t="s">
+      <c r="E6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="228" t="s">
+      <c r="F6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="228" t="s">
+      <c r="G6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="228" t="s">
+      <c r="H6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="228" t="s">
+      <c r="I6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="228" t="s">
+      <c r="J6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="228" t="s">
+      <c r="K6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="228" t="s">
+      <c r="L6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="228" t="s">
+      <c r="M6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="227" t="s">
+      <c r="N6" s="209" t="s">
         <v>500</v>
       </c>
     </row>
@@ -39558,41 +39558,41 @@
       <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="226">
+      <c r="C7" s="208">
         <v>6</v>
       </c>
-      <c r="D7" s="226">
+      <c r="D7" s="208">
         <v>6</v>
       </c>
-      <c r="E7" s="226">
+      <c r="E7" s="208">
         <v>6</v>
       </c>
-      <c r="F7" s="226">
+      <c r="F7" s="208">
         <v>7</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="208">
         <v>6</v>
       </c>
-      <c r="H7" s="226">
+      <c r="H7" s="208">
         <v>8</v>
       </c>
-      <c r="I7" s="226">
+      <c r="I7" s="208">
         <v>7</v>
       </c>
-      <c r="J7" s="226">
+      <c r="J7" s="208">
         <v>6</v>
       </c>
-      <c r="K7" s="226">
+      <c r="K7" s="208">
         <v>6</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="208">
         <v>6</v>
       </c>
-      <c r="M7" s="226">
+      <c r="M7" s="208">
         <v>5</v>
       </c>
-      <c r="N7" s="222">
-        <f>AVERAGE(C7:M7)</f>
+      <c r="N7" s="204">
+        <f t="shared" ref="N7:N18" si="0">AVERAGE(C7:M7)</f>
         <v>6.2727272727272725</v>
       </c>
     </row>
@@ -39603,41 +39603,41 @@
       <c r="B8" s="65">
         <v>2</v>
       </c>
-      <c r="C8" s="225">
+      <c r="C8" s="207">
         <v>6</v>
       </c>
-      <c r="D8" s="225">
+      <c r="D8" s="207">
         <v>7</v>
       </c>
-      <c r="E8" s="225">
+      <c r="E8" s="207">
         <v>7</v>
       </c>
-      <c r="F8" s="225">
+      <c r="F8" s="207">
         <v>7</v>
       </c>
-      <c r="G8" s="225">
+      <c r="G8" s="207">
         <v>8</v>
       </c>
-      <c r="H8" s="225">
+      <c r="H8" s="207">
         <v>7</v>
       </c>
-      <c r="I8" s="225">
+      <c r="I8" s="207">
         <v>7</v>
       </c>
-      <c r="J8" s="225">
+      <c r="J8" s="207">
         <v>8</v>
       </c>
-      <c r="K8" s="225">
+      <c r="K8" s="207">
         <v>8</v>
       </c>
-      <c r="L8" s="225">
+      <c r="L8" s="207">
         <v>7</v>
       </c>
-      <c r="M8" s="225">
+      <c r="M8" s="207">
         <v>7</v>
       </c>
-      <c r="N8" s="222">
-        <f>AVERAGE(C8:M8)</f>
+      <c r="N8" s="204">
+        <f t="shared" si="0"/>
         <v>7.1818181818181817</v>
       </c>
     </row>
@@ -39648,41 +39648,41 @@
       <c r="B9" s="65">
         <v>3</v>
       </c>
-      <c r="C9" s="225">
+      <c r="C9" s="207">
         <v>7</v>
       </c>
-      <c r="D9" s="225">
+      <c r="D9" s="207">
         <v>8</v>
       </c>
-      <c r="E9" s="225">
+      <c r="E9" s="207">
         <v>8</v>
       </c>
-      <c r="F9" s="225">
+      <c r="F9" s="207">
         <v>9</v>
       </c>
-      <c r="G9" s="225">
+      <c r="G9" s="207">
         <v>7</v>
       </c>
-      <c r="H9" s="225">
+      <c r="H9" s="207">
         <v>7</v>
       </c>
-      <c r="I9" s="225">
+      <c r="I9" s="207">
         <v>8</v>
       </c>
-      <c r="J9" s="225">
+      <c r="J9" s="207">
         <v>7</v>
       </c>
-      <c r="K9" s="225">
+      <c r="K9" s="207">
         <v>7</v>
       </c>
-      <c r="L9" s="225">
+      <c r="L9" s="207">
         <v>6</v>
       </c>
-      <c r="M9" s="225">
+      <c r="M9" s="207">
         <v>6</v>
       </c>
-      <c r="N9" s="222">
-        <f>AVERAGE(C9:M9)</f>
+      <c r="N9" s="204">
+        <f t="shared" si="0"/>
         <v>7.2727272727272725</v>
       </c>
     </row>
@@ -39690,44 +39690,44 @@
       <c r="A10" t="s">
         <v>499</v>
       </c>
-      <c r="B10" s="224">
+      <c r="B10" s="206">
         <v>4</v>
       </c>
-      <c r="C10" s="223">
+      <c r="C10" s="205">
         <v>5</v>
       </c>
-      <c r="D10" s="223">
+      <c r="D10" s="205">
         <v>5</v>
       </c>
-      <c r="E10" s="223">
+      <c r="E10" s="205">
         <v>6</v>
       </c>
-      <c r="F10" s="223">
+      <c r="F10" s="205">
         <v>9</v>
       </c>
-      <c r="G10" s="223">
+      <c r="G10" s="205">
         <v>7</v>
       </c>
-      <c r="H10" s="223">
+      <c r="H10" s="205">
         <v>7</v>
       </c>
-      <c r="I10" s="223">
+      <c r="I10" s="205">
         <v>7</v>
       </c>
-      <c r="J10" s="223">
+      <c r="J10" s="205">
         <v>8</v>
       </c>
-      <c r="K10" s="223">
+      <c r="K10" s="205">
         <v>7</v>
       </c>
-      <c r="L10" s="223">
+      <c r="L10" s="205">
         <v>6</v>
       </c>
-      <c r="M10" s="223">
+      <c r="M10" s="205">
         <v>6</v>
       </c>
-      <c r="N10" s="222">
-        <f>AVERAGE(C10:M10)</f>
+      <c r="N10" s="204">
+        <f t="shared" si="0"/>
         <v>6.6363636363636367</v>
       </c>
     </row>
@@ -39735,44 +39735,44 @@
       <c r="A11" t="s">
         <v>498</v>
       </c>
-      <c r="B11" s="224">
+      <c r="B11" s="206">
         <v>5</v>
       </c>
-      <c r="C11" s="223">
+      <c r="C11" s="205">
         <v>8</v>
       </c>
-      <c r="D11" s="223">
+      <c r="D11" s="205">
         <v>7</v>
       </c>
-      <c r="E11" s="223">
+      <c r="E11" s="205">
         <v>7</v>
       </c>
-      <c r="F11" s="223">
+      <c r="F11" s="205">
         <v>8</v>
       </c>
-      <c r="G11" s="223">
+      <c r="G11" s="205">
         <v>7</v>
       </c>
-      <c r="H11" s="223">
+      <c r="H11" s="205">
         <v>8</v>
       </c>
-      <c r="I11" s="223">
+      <c r="I11" s="205">
         <v>8</v>
       </c>
-      <c r="J11" s="223">
+      <c r="J11" s="205">
         <v>7</v>
       </c>
-      <c r="K11" s="223">
+      <c r="K11" s="205">
         <v>6</v>
       </c>
-      <c r="L11" s="223">
+      <c r="L11" s="205">
         <v>7</v>
       </c>
-      <c r="M11" s="223">
+      <c r="M11" s="205">
         <v>6</v>
       </c>
-      <c r="N11" s="222">
-        <f>AVERAGE(C11:M11)</f>
+      <c r="N11" s="204">
+        <f t="shared" si="0"/>
         <v>7.1818181818181817</v>
       </c>
     </row>
@@ -39780,44 +39780,44 @@
       <c r="A12" t="s">
         <v>497</v>
       </c>
-      <c r="B12" s="224">
+      <c r="B12" s="206">
         <v>6</v>
       </c>
-      <c r="C12" s="223">
+      <c r="C12" s="205">
         <v>6</v>
       </c>
-      <c r="D12" s="223">
+      <c r="D12" s="205">
         <v>5</v>
       </c>
-      <c r="E12" s="223">
+      <c r="E12" s="205">
         <v>6</v>
       </c>
-      <c r="F12" s="223">
+      <c r="F12" s="205">
         <v>6</v>
       </c>
-      <c r="G12" s="223">
+      <c r="G12" s="205">
         <v>7</v>
       </c>
-      <c r="H12" s="223">
+      <c r="H12" s="205">
         <v>7</v>
       </c>
-      <c r="I12" s="223">
+      <c r="I12" s="205">
         <v>8</v>
       </c>
-      <c r="J12" s="223">
+      <c r="J12" s="205">
         <v>7</v>
       </c>
-      <c r="K12" s="223">
+      <c r="K12" s="205">
         <v>8</v>
       </c>
-      <c r="L12" s="223">
+      <c r="L12" s="205">
         <v>7</v>
       </c>
-      <c r="M12" s="223">
+      <c r="M12" s="205">
         <v>7</v>
       </c>
-      <c r="N12" s="222">
-        <f>AVERAGE(C12:M12)</f>
+      <c r="N12" s="204">
+        <f t="shared" si="0"/>
         <v>6.7272727272727275</v>
       </c>
     </row>
@@ -39825,44 +39825,44 @@
       <c r="A13" t="s">
         <v>495</v>
       </c>
-      <c r="B13" s="224">
+      <c r="B13" s="206">
         <v>7</v>
       </c>
-      <c r="C13" s="223">
+      <c r="C13" s="205">
         <v>6</v>
       </c>
-      <c r="D13" s="223">
+      <c r="D13" s="205">
         <v>7</v>
       </c>
-      <c r="E13" s="223">
+      <c r="E13" s="205">
         <v>6</v>
       </c>
-      <c r="F13" s="223">
+      <c r="F13" s="205">
         <v>6</v>
       </c>
-      <c r="G13" s="223">
+      <c r="G13" s="205">
         <v>6</v>
       </c>
-      <c r="H13" s="223">
+      <c r="H13" s="205">
         <v>7</v>
       </c>
-      <c r="I13" s="223">
+      <c r="I13" s="205">
         <v>7</v>
       </c>
-      <c r="J13" s="223">
+      <c r="J13" s="205">
         <v>6</v>
       </c>
-      <c r="K13" s="223">
+      <c r="K13" s="205">
         <v>6</v>
       </c>
-      <c r="L13" s="223">
+      <c r="L13" s="205">
         <v>7</v>
       </c>
-      <c r="M13" s="223">
+      <c r="M13" s="205">
         <v>5</v>
       </c>
-      <c r="N13" s="222">
-        <f>AVERAGE(C13:M13)</f>
+      <c r="N13" s="204">
+        <f t="shared" si="0"/>
         <v>6.2727272727272725</v>
       </c>
     </row>
@@ -39870,44 +39870,44 @@
       <c r="A14" t="s">
         <v>496</v>
       </c>
-      <c r="B14" s="224">
+      <c r="B14" s="206">
         <v>8</v>
       </c>
-      <c r="C14" s="223">
+      <c r="C14" s="205">
         <v>6</v>
       </c>
-      <c r="D14" s="223">
+      <c r="D14" s="205">
         <v>6</v>
       </c>
-      <c r="E14" s="223">
+      <c r="E14" s="205">
         <v>8</v>
       </c>
-      <c r="F14" s="223">
+      <c r="F14" s="205">
         <v>7</v>
       </c>
-      <c r="G14" s="223">
+      <c r="G14" s="205">
         <v>7</v>
       </c>
-      <c r="H14" s="223">
+      <c r="H14" s="205">
         <v>8</v>
       </c>
-      <c r="I14" s="223">
+      <c r="I14" s="205">
         <v>7</v>
       </c>
-      <c r="J14" s="223">
+      <c r="J14" s="205">
         <v>6</v>
       </c>
-      <c r="K14" s="223">
+      <c r="K14" s="205">
         <v>6</v>
       </c>
-      <c r="L14" s="223">
+      <c r="L14" s="205">
         <v>7</v>
       </c>
-      <c r="M14" s="223">
+      <c r="M14" s="205">
         <v>7</v>
       </c>
-      <c r="N14" s="222">
-        <f>AVERAGE(C14:M14)</f>
+      <c r="N14" s="204">
+        <f t="shared" si="0"/>
         <v>6.8181818181818183</v>
       </c>
     </row>
@@ -39915,44 +39915,44 @@
       <c r="A15" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="224">
+      <c r="B15" s="206">
         <v>9</v>
       </c>
-      <c r="C15" s="223">
+      <c r="C15" s="205">
         <v>6</v>
       </c>
-      <c r="D15" s="223">
+      <c r="D15" s="205">
         <v>7</v>
       </c>
-      <c r="E15" s="223">
+      <c r="E15" s="205">
         <v>8</v>
       </c>
-      <c r="F15" s="223">
+      <c r="F15" s="205">
         <v>6</v>
       </c>
-      <c r="G15" s="223">
+      <c r="G15" s="205">
         <v>7</v>
       </c>
-      <c r="H15" s="223">
+      <c r="H15" s="205">
         <v>8</v>
       </c>
-      <c r="I15" s="223">
+      <c r="I15" s="205">
         <v>7</v>
       </c>
-      <c r="J15" s="223">
+      <c r="J15" s="205">
         <v>6</v>
       </c>
-      <c r="K15" s="223">
+      <c r="K15" s="205">
         <v>7</v>
       </c>
-      <c r="L15" s="223">
+      <c r="L15" s="205">
         <v>6</v>
       </c>
-      <c r="M15" s="223">
+      <c r="M15" s="205">
         <v>5</v>
       </c>
-      <c r="N15" s="222">
-        <f>AVERAGE(C15:M15)</f>
+      <c r="N15" s="204">
+        <f t="shared" si="0"/>
         <v>6.6363636363636367</v>
       </c>
     </row>
@@ -39960,44 +39960,44 @@
       <c r="A16" t="s">
         <v>495</v>
       </c>
-      <c r="B16" s="224">
+      <c r="B16" s="206">
         <v>10</v>
       </c>
-      <c r="C16" s="223">
+      <c r="C16" s="205">
         <v>4</v>
       </c>
-      <c r="D16" s="223">
+      <c r="D16" s="205">
         <v>6</v>
       </c>
-      <c r="E16" s="223">
+      <c r="E16" s="205">
         <v>6</v>
       </c>
-      <c r="F16" s="223">
+      <c r="F16" s="205">
         <v>7</v>
       </c>
-      <c r="G16" s="223">
+      <c r="G16" s="205">
         <v>7</v>
       </c>
-      <c r="H16" s="223">
+      <c r="H16" s="205">
         <v>6</v>
       </c>
-      <c r="I16" s="223">
+      <c r="I16" s="205">
         <v>6</v>
       </c>
-      <c r="J16" s="223">
+      <c r="J16" s="205">
         <v>7</v>
       </c>
-      <c r="K16" s="223">
+      <c r="K16" s="205">
         <v>6</v>
       </c>
-      <c r="L16" s="223">
+      <c r="L16" s="205">
         <v>6</v>
       </c>
-      <c r="M16" s="223">
+      <c r="M16" s="205">
         <v>6</v>
       </c>
-      <c r="N16" s="222">
-        <f>AVERAGE(C16:M16)</f>
+      <c r="N16" s="204">
+        <f t="shared" si="0"/>
         <v>6.0909090909090908</v>
       </c>
     </row>
@@ -40005,44 +40005,44 @@
       <c r="A17" t="s">
         <v>496</v>
       </c>
-      <c r="B17" s="224">
+      <c r="B17" s="206">
         <v>11</v>
       </c>
-      <c r="C17" s="223">
+      <c r="C17" s="205">
         <v>6</v>
       </c>
-      <c r="D17" s="223">
+      <c r="D17" s="205">
         <v>6</v>
       </c>
-      <c r="E17" s="223">
+      <c r="E17" s="205">
         <v>7</v>
       </c>
-      <c r="F17" s="223">
+      <c r="F17" s="205">
         <v>8</v>
       </c>
-      <c r="G17" s="223">
+      <c r="G17" s="205">
         <v>8</v>
       </c>
-      <c r="H17" s="223">
+      <c r="H17" s="205">
         <v>7</v>
       </c>
-      <c r="I17" s="223">
+      <c r="I17" s="205">
         <v>6</v>
       </c>
-      <c r="J17" s="223">
+      <c r="J17" s="205">
         <v>6</v>
       </c>
-      <c r="K17" s="223">
+      <c r="K17" s="205">
         <v>7</v>
       </c>
-      <c r="L17" s="223">
+      <c r="L17" s="205">
         <v>6</v>
       </c>
-      <c r="M17" s="223">
+      <c r="M17" s="205">
         <v>7</v>
       </c>
-      <c r="N17" s="222">
-        <f>AVERAGE(C17:M17)</f>
+      <c r="N17" s="204">
+        <f t="shared" si="0"/>
         <v>6.7272727272727275</v>
       </c>
     </row>
@@ -40050,44 +40050,44 @@
       <c r="A18" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="224">
+      <c r="B18" s="206">
         <v>12</v>
       </c>
-      <c r="C18" s="223">
+      <c r="C18" s="205">
         <v>5</v>
       </c>
-      <c r="D18" s="223">
+      <c r="D18" s="205">
         <v>5</v>
       </c>
-      <c r="E18" s="223">
+      <c r="E18" s="205">
         <v>6</v>
       </c>
-      <c r="F18" s="223">
+      <c r="F18" s="205">
         <v>6</v>
       </c>
-      <c r="G18" s="223">
+      <c r="G18" s="205">
         <v>7</v>
       </c>
-      <c r="H18" s="223">
+      <c r="H18" s="205">
         <v>7</v>
       </c>
-      <c r="I18" s="223">
+      <c r="I18" s="205">
         <v>6</v>
       </c>
-      <c r="J18" s="223">
+      <c r="J18" s="205">
         <v>7</v>
       </c>
-      <c r="K18" s="223">
+      <c r="K18" s="205">
         <v>6</v>
       </c>
-      <c r="L18" s="223">
+      <c r="L18" s="205">
         <v>8</v>
       </c>
-      <c r="M18" s="223">
+      <c r="M18" s="205">
         <v>6</v>
       </c>
-      <c r="N18" s="222">
-        <f>AVERAGE(C18:M18)</f>
+      <c r="N18" s="204">
+        <f t="shared" si="0"/>
         <v>6.2727272727272725</v>
       </c>
     </row>
@@ -40123,15 +40123,15 @@
       <c r="E1" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="F1" s="235">
+      <c r="F1" s="215">
         <v>45120</v>
       </c>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -40150,75 +40150,75 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>501</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="231" t="s">
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="231"/>
-      <c r="L4" s="231"/>
-      <c r="M4" s="230"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="212"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="228" t="s">
+      <c r="E6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="228" t="s">
+      <c r="F6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="228" t="s">
+      <c r="G6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="228" t="s">
+      <c r="H6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="228" t="s">
+      <c r="I6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="228" t="s">
+      <c r="J6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="228" t="s">
+      <c r="K6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="228" t="s">
+      <c r="L6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="228" t="s">
+      <c r="M6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="227" t="s">
+      <c r="N6" s="209" t="s">
         <v>500</v>
       </c>
     </row>
@@ -40229,41 +40229,41 @@
       <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="226">
+      <c r="C7" s="208">
         <v>6</v>
       </c>
-      <c r="D7" s="226">
+      <c r="D7" s="208">
         <v>6</v>
       </c>
-      <c r="E7" s="226">
+      <c r="E7" s="208">
         <v>6</v>
       </c>
-      <c r="F7" s="226">
+      <c r="F7" s="208">
         <v>5</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="208">
         <v>7</v>
       </c>
-      <c r="H7" s="226">
+      <c r="H7" s="208">
         <v>7</v>
       </c>
-      <c r="I7" s="226">
+      <c r="I7" s="208">
         <v>6</v>
       </c>
-      <c r="J7" s="226">
+      <c r="J7" s="208">
         <v>5</v>
       </c>
-      <c r="K7" s="226">
+      <c r="K7" s="208">
         <v>6</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="208">
         <v>6</v>
       </c>
-      <c r="M7" s="226">
+      <c r="M7" s="208">
         <v>5</v>
       </c>
-      <c r="N7" s="222">
-        <f>AVERAGE(C7:M7)</f>
+      <c r="N7" s="204">
+        <f t="shared" ref="N7:N18" si="0">AVERAGE(C7:M7)</f>
         <v>5.9090909090909092</v>
       </c>
     </row>
@@ -40274,41 +40274,41 @@
       <c r="B8" s="65">
         <v>2</v>
       </c>
-      <c r="C8" s="225">
+      <c r="C8" s="207">
         <v>6</v>
       </c>
-      <c r="D8" s="225">
+      <c r="D8" s="207">
         <v>5</v>
       </c>
-      <c r="E8" s="225">
+      <c r="E8" s="207">
         <v>7</v>
       </c>
-      <c r="F8" s="225">
+      <c r="F8" s="207">
         <v>7</v>
       </c>
-      <c r="G8" s="225">
+      <c r="G8" s="207">
         <v>8</v>
       </c>
-      <c r="H8" s="225">
+      <c r="H8" s="207">
         <v>7</v>
       </c>
-      <c r="I8" s="225">
+      <c r="I8" s="207">
         <v>6</v>
       </c>
-      <c r="J8" s="225">
+      <c r="J8" s="207">
         <v>7</v>
       </c>
-      <c r="K8" s="225">
+      <c r="K8" s="207">
         <v>7</v>
       </c>
-      <c r="L8" s="225">
+      <c r="L8" s="207">
         <v>8</v>
       </c>
-      <c r="M8" s="225">
+      <c r="M8" s="207">
         <v>7</v>
       </c>
-      <c r="N8" s="222">
-        <f>AVERAGE(C8:M8)</f>
+      <c r="N8" s="204">
+        <f t="shared" si="0"/>
         <v>6.8181818181818183</v>
       </c>
     </row>
@@ -40319,41 +40319,41 @@
       <c r="B9" s="65">
         <v>3</v>
       </c>
-      <c r="C9" s="225">
+      <c r="C9" s="207">
         <v>7</v>
       </c>
-      <c r="D9" s="225">
+      <c r="D9" s="207">
         <v>7</v>
       </c>
-      <c r="E9" s="225">
+      <c r="E9" s="207">
         <v>6</v>
       </c>
-      <c r="F9" s="225">
+      <c r="F9" s="207">
         <v>8</v>
       </c>
-      <c r="G9" s="225">
+      <c r="G9" s="207">
         <v>8</v>
       </c>
-      <c r="H9" s="225">
+      <c r="H9" s="207">
         <v>7</v>
       </c>
-      <c r="I9" s="225">
+      <c r="I9" s="207">
         <v>5</v>
       </c>
-      <c r="J9" s="225">
+      <c r="J9" s="207">
         <v>6</v>
       </c>
-      <c r="K9" s="225">
+      <c r="K9" s="207">
         <v>6</v>
       </c>
-      <c r="L9" s="225">
+      <c r="L9" s="207">
         <v>7</v>
       </c>
-      <c r="M9" s="225">
+      <c r="M9" s="207">
         <v>7</v>
       </c>
-      <c r="N9" s="222">
-        <f>AVERAGE(C9:M9)</f>
+      <c r="N9" s="204">
+        <f t="shared" si="0"/>
         <v>6.7272727272727275</v>
       </c>
     </row>
@@ -40361,44 +40361,44 @@
       <c r="A10" t="s">
         <v>499</v>
       </c>
-      <c r="B10" s="224">
+      <c r="B10" s="206">
         <v>4</v>
       </c>
-      <c r="C10" s="223">
+      <c r="C10" s="205">
         <v>5</v>
       </c>
-      <c r="D10" s="223">
+      <c r="D10" s="205">
         <v>5</v>
       </c>
-      <c r="E10" s="223">
+      <c r="E10" s="205">
         <v>6</v>
       </c>
-      <c r="F10" s="223">
+      <c r="F10" s="205">
         <v>6</v>
       </c>
-      <c r="G10" s="223">
+      <c r="G10" s="205">
         <v>6</v>
       </c>
-      <c r="H10" s="223">
+      <c r="H10" s="205">
         <v>7</v>
       </c>
-      <c r="I10" s="223">
+      <c r="I10" s="205">
         <v>6</v>
       </c>
-      <c r="J10" s="223">
+      <c r="J10" s="205">
         <v>6</v>
       </c>
-      <c r="K10" s="223">
+      <c r="K10" s="205">
         <v>5</v>
       </c>
-      <c r="L10" s="223">
+      <c r="L10" s="205">
         <v>6</v>
       </c>
-      <c r="M10" s="223">
+      <c r="M10" s="205">
         <v>6</v>
       </c>
-      <c r="N10" s="222">
-        <f>AVERAGE(C10:M10)</f>
+      <c r="N10" s="204">
+        <f t="shared" si="0"/>
         <v>5.8181818181818183</v>
       </c>
     </row>
@@ -40406,44 +40406,44 @@
       <c r="A11" t="s">
         <v>498</v>
       </c>
-      <c r="B11" s="224">
+      <c r="B11" s="206">
         <v>5</v>
       </c>
-      <c r="C11" s="223">
+      <c r="C11" s="205">
         <v>7</v>
       </c>
-      <c r="D11" s="223">
+      <c r="D11" s="205">
         <v>6</v>
       </c>
-      <c r="E11" s="223">
+      <c r="E11" s="205">
         <v>7</v>
       </c>
-      <c r="F11" s="223">
+      <c r="F11" s="205">
         <v>6</v>
       </c>
-      <c r="G11" s="223">
+      <c r="G11" s="205">
         <v>7</v>
       </c>
-      <c r="H11" s="223">
+      <c r="H11" s="205">
         <v>6</v>
       </c>
-      <c r="I11" s="223">
+      <c r="I11" s="205">
         <v>7</v>
       </c>
-      <c r="J11" s="223">
+      <c r="J11" s="205">
         <v>8</v>
       </c>
-      <c r="K11" s="223">
+      <c r="K11" s="205">
         <v>6</v>
       </c>
-      <c r="L11" s="223">
+      <c r="L11" s="205">
         <v>7</v>
       </c>
-      <c r="M11" s="223">
+      <c r="M11" s="205">
         <v>6</v>
       </c>
-      <c r="N11" s="222">
-        <f>AVERAGE(C11:M11)</f>
+      <c r="N11" s="204">
+        <f t="shared" si="0"/>
         <v>6.6363636363636367</v>
       </c>
     </row>
@@ -40451,44 +40451,44 @@
       <c r="A12" t="s">
         <v>497</v>
       </c>
-      <c r="B12" s="224">
+      <c r="B12" s="206">
         <v>6</v>
       </c>
-      <c r="C12" s="223">
+      <c r="C12" s="205">
         <v>4</v>
       </c>
-      <c r="D12" s="223">
+      <c r="D12" s="205">
         <v>6</v>
       </c>
-      <c r="E12" s="223">
+      <c r="E12" s="205">
         <v>6</v>
       </c>
-      <c r="F12" s="223">
+      <c r="F12" s="205">
         <v>7</v>
       </c>
-      <c r="G12" s="223">
+      <c r="G12" s="205">
         <v>6</v>
       </c>
-      <c r="H12" s="223">
+      <c r="H12" s="205">
         <v>6</v>
       </c>
-      <c r="I12" s="223">
+      <c r="I12" s="205">
         <v>5</v>
       </c>
-      <c r="J12" s="223">
+      <c r="J12" s="205">
         <v>5</v>
       </c>
-      <c r="K12" s="223">
+      <c r="K12" s="205">
         <v>6</v>
       </c>
-      <c r="L12" s="223">
+      <c r="L12" s="205">
         <v>6</v>
       </c>
-      <c r="M12" s="223">
+      <c r="M12" s="205">
         <v>5</v>
       </c>
-      <c r="N12" s="222">
-        <f>AVERAGE(C12:M12)</f>
+      <c r="N12" s="204">
+        <f t="shared" si="0"/>
         <v>5.6363636363636367</v>
       </c>
     </row>
@@ -40496,44 +40496,44 @@
       <c r="A13" t="s">
         <v>495</v>
       </c>
-      <c r="B13" s="224">
+      <c r="B13" s="206">
         <v>7</v>
       </c>
-      <c r="C13" s="223">
+      <c r="C13" s="205">
         <v>5</v>
       </c>
-      <c r="D13" s="223">
+      <c r="D13" s="205">
         <v>5</v>
       </c>
-      <c r="E13" s="223">
+      <c r="E13" s="205">
         <v>6</v>
       </c>
-      <c r="F13" s="223">
+      <c r="F13" s="205">
         <v>6</v>
       </c>
-      <c r="G13" s="223">
+      <c r="G13" s="205">
         <v>7</v>
       </c>
-      <c r="H13" s="223">
+      <c r="H13" s="205">
         <v>6</v>
       </c>
-      <c r="I13" s="223">
+      <c r="I13" s="205">
         <v>5</v>
       </c>
-      <c r="J13" s="223">
+      <c r="J13" s="205">
         <v>6</v>
       </c>
-      <c r="K13" s="223">
+      <c r="K13" s="205">
         <v>5</v>
       </c>
-      <c r="L13" s="223">
+      <c r="L13" s="205">
         <v>4</v>
       </c>
-      <c r="M13" s="223">
+      <c r="M13" s="205">
         <v>4</v>
       </c>
-      <c r="N13" s="222">
-        <f>AVERAGE(C13:M13)</f>
+      <c r="N13" s="204">
+        <f t="shared" si="0"/>
         <v>5.3636363636363633</v>
       </c>
     </row>
@@ -40541,44 +40541,44 @@
       <c r="A14" t="s">
         <v>496</v>
       </c>
-      <c r="B14" s="224">
+      <c r="B14" s="206">
         <v>8</v>
       </c>
-      <c r="C14" s="223">
+      <c r="C14" s="205">
         <v>5</v>
       </c>
-      <c r="D14" s="223">
+      <c r="D14" s="205">
         <v>6</v>
       </c>
-      <c r="E14" s="223">
+      <c r="E14" s="205">
         <v>6</v>
       </c>
-      <c r="F14" s="223">
+      <c r="F14" s="205">
         <v>7</v>
       </c>
-      <c r="G14" s="223">
+      <c r="G14" s="205">
         <v>7</v>
       </c>
-      <c r="H14" s="223">
+      <c r="H14" s="205">
         <v>7</v>
       </c>
-      <c r="I14" s="223">
+      <c r="I14" s="205">
         <v>6</v>
       </c>
-      <c r="J14" s="223">
+      <c r="J14" s="205">
         <v>5</v>
       </c>
-      <c r="K14" s="223">
+      <c r="K14" s="205">
         <v>5</v>
       </c>
-      <c r="L14" s="223">
+      <c r="L14" s="205">
         <v>5</v>
       </c>
-      <c r="M14" s="223">
+      <c r="M14" s="205">
         <v>5</v>
       </c>
-      <c r="N14" s="222">
-        <f>AVERAGE(C14:M14)</f>
+      <c r="N14" s="204">
+        <f t="shared" si="0"/>
         <v>5.8181818181818183</v>
       </c>
     </row>
@@ -40586,44 +40586,44 @@
       <c r="A15" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="224">
+      <c r="B15" s="206">
         <v>9</v>
       </c>
-      <c r="C15" s="223">
+      <c r="C15" s="205">
         <v>6</v>
       </c>
-      <c r="D15" s="223">
+      <c r="D15" s="205">
         <v>5</v>
       </c>
-      <c r="E15" s="223">
+      <c r="E15" s="205">
         <v>7</v>
       </c>
-      <c r="F15" s="223">
+      <c r="F15" s="205">
         <v>6</v>
       </c>
-      <c r="G15" s="223">
+      <c r="G15" s="205">
         <v>6</v>
       </c>
-      <c r="H15" s="223">
+      <c r="H15" s="205">
         <v>7</v>
       </c>
-      <c r="I15" s="223">
+      <c r="I15" s="205">
         <v>8</v>
       </c>
-      <c r="J15" s="223">
+      <c r="J15" s="205">
         <v>7</v>
       </c>
-      <c r="K15" s="223">
+      <c r="K15" s="205">
         <v>6</v>
       </c>
-      <c r="L15" s="223">
+      <c r="L15" s="205">
         <v>5</v>
       </c>
-      <c r="M15" s="223">
+      <c r="M15" s="205">
         <v>4</v>
       </c>
-      <c r="N15" s="222">
-        <f>AVERAGE(C15:M15)</f>
+      <c r="N15" s="204">
+        <f t="shared" si="0"/>
         <v>6.0909090909090908</v>
       </c>
     </row>
@@ -40631,44 +40631,44 @@
       <c r="A16" t="s">
         <v>495</v>
       </c>
-      <c r="B16" s="224">
+      <c r="B16" s="206">
         <v>10</v>
       </c>
-      <c r="C16" s="223">
+      <c r="C16" s="205">
         <v>4</v>
       </c>
-      <c r="D16" s="223">
+      <c r="D16" s="205">
         <v>4</v>
       </c>
-      <c r="E16" s="223">
+      <c r="E16" s="205">
         <v>6</v>
       </c>
-      <c r="F16" s="223">
+      <c r="F16" s="205">
         <v>5</v>
       </c>
-      <c r="G16" s="223">
+      <c r="G16" s="205">
         <v>6</v>
       </c>
-      <c r="H16" s="223">
+      <c r="H16" s="205">
         <v>6</v>
       </c>
-      <c r="I16" s="223">
+      <c r="I16" s="205">
         <v>7</v>
       </c>
-      <c r="J16" s="223">
+      <c r="J16" s="205">
         <v>6</v>
       </c>
-      <c r="K16" s="223">
+      <c r="K16" s="205">
         <v>6</v>
       </c>
-      <c r="L16" s="223">
+      <c r="L16" s="205">
         <v>5</v>
       </c>
-      <c r="M16" s="223">
+      <c r="M16" s="205">
         <v>6</v>
       </c>
-      <c r="N16" s="222">
-        <f>AVERAGE(C16:M16)</f>
+      <c r="N16" s="204">
+        <f t="shared" si="0"/>
         <v>5.5454545454545459</v>
       </c>
     </row>
@@ -40676,44 +40676,44 @@
       <c r="A17" t="s">
         <v>496</v>
       </c>
-      <c r="B17" s="224">
+      <c r="B17" s="206">
         <v>11</v>
       </c>
-      <c r="C17" s="223">
+      <c r="C17" s="205">
         <v>6</v>
       </c>
-      <c r="D17" s="223">
+      <c r="D17" s="205">
         <v>7</v>
       </c>
-      <c r="E17" s="223">
+      <c r="E17" s="205">
         <v>6</v>
       </c>
-      <c r="F17" s="223">
+      <c r="F17" s="205">
         <v>5</v>
       </c>
-      <c r="G17" s="223">
+      <c r="G17" s="205">
         <v>6</v>
       </c>
-      <c r="H17" s="223">
+      <c r="H17" s="205">
         <v>7</v>
       </c>
-      <c r="I17" s="223">
+      <c r="I17" s="205">
         <v>6</v>
       </c>
-      <c r="J17" s="223">
+      <c r="J17" s="205">
         <v>6</v>
       </c>
-      <c r="K17" s="223">
+      <c r="K17" s="205">
         <v>6</v>
       </c>
-      <c r="L17" s="223">
+      <c r="L17" s="205">
         <v>7</v>
       </c>
-      <c r="M17" s="223">
+      <c r="M17" s="205">
         <v>6</v>
       </c>
-      <c r="N17" s="222">
-        <f>AVERAGE(C17:M17)</f>
+      <c r="N17" s="204">
+        <f t="shared" si="0"/>
         <v>6.1818181818181817</v>
       </c>
     </row>
@@ -40721,44 +40721,44 @@
       <c r="A18" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="224">
+      <c r="B18" s="206">
         <v>12</v>
       </c>
-      <c r="C18" s="223">
+      <c r="C18" s="205">
         <v>3</v>
       </c>
-      <c r="D18" s="223">
+      <c r="D18" s="205">
         <v>4</v>
       </c>
-      <c r="E18" s="223">
+      <c r="E18" s="205">
         <v>6</v>
       </c>
-      <c r="F18" s="223">
+      <c r="F18" s="205">
         <v>6</v>
       </c>
-      <c r="G18" s="223">
+      <c r="G18" s="205">
         <v>6</v>
       </c>
-      <c r="H18" s="223">
+      <c r="H18" s="205">
         <v>7</v>
       </c>
-      <c r="I18" s="223">
+      <c r="I18" s="205">
         <v>6</v>
       </c>
-      <c r="J18" s="223">
+      <c r="J18" s="205">
         <v>6</v>
       </c>
-      <c r="K18" s="223">
+      <c r="K18" s="205">
         <v>7</v>
       </c>
-      <c r="L18" s="223">
+      <c r="L18" s="205">
         <v>6</v>
       </c>
-      <c r="M18" s="223">
+      <c r="M18" s="205">
         <v>6</v>
       </c>
-      <c r="N18" s="222">
-        <f>AVERAGE(C18:M18)</f>
+      <c r="N18" s="204">
+        <f t="shared" si="0"/>
         <v>5.7272727272727275</v>
       </c>
     </row>
@@ -40794,15 +40794,15 @@
       <c r="E1" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="F1" s="235">
+      <c r="F1" s="215">
         <v>45127</v>
       </c>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -40821,75 +40821,75 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>501</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="231" t="s">
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="231"/>
-      <c r="L4" s="231"/>
-      <c r="M4" s="230"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="212"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="228" t="s">
+      <c r="E6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="228" t="s">
+      <c r="F6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="228" t="s">
+      <c r="G6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="228" t="s">
+      <c r="H6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="228" t="s">
+      <c r="I6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="228" t="s">
+      <c r="J6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="228" t="s">
+      <c r="K6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="228" t="s">
+      <c r="L6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="228" t="s">
+      <c r="M6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="227" t="s">
+      <c r="N6" s="209" t="s">
         <v>500</v>
       </c>
     </row>
@@ -40900,41 +40900,41 @@
       <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="226">
+      <c r="C7" s="208">
         <v>4</v>
       </c>
-      <c r="D7" s="226">
+      <c r="D7" s="208">
         <v>5</v>
       </c>
-      <c r="E7" s="226">
+      <c r="E7" s="208">
         <v>4</v>
       </c>
-      <c r="F7" s="226">
+      <c r="F7" s="208">
         <v>5</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="208">
         <v>6</v>
       </c>
-      <c r="H7" s="226">
+      <c r="H7" s="208">
         <v>5</v>
       </c>
-      <c r="I7" s="226">
+      <c r="I7" s="208">
         <v>5</v>
       </c>
-      <c r="J7" s="226">
+      <c r="J7" s="208">
         <v>5</v>
       </c>
-      <c r="K7" s="226">
+      <c r="K7" s="208">
         <v>4</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="208">
         <v>5</v>
       </c>
-      <c r="M7" s="226">
+      <c r="M7" s="208">
         <v>4</v>
       </c>
-      <c r="N7" s="222">
-        <f>AVERAGE(C7:M7)</f>
+      <c r="N7" s="204">
+        <f t="shared" ref="N7:N18" si="0">AVERAGE(C7:M7)</f>
         <v>4.7272727272727275</v>
       </c>
     </row>
@@ -40945,41 +40945,41 @@
       <c r="B8" s="65">
         <v>2</v>
       </c>
-      <c r="C8" s="225">
+      <c r="C8" s="207">
         <v>3</v>
       </c>
-      <c r="D8" s="225">
+      <c r="D8" s="207">
         <v>4</v>
       </c>
-      <c r="E8" s="225">
+      <c r="E8" s="207">
         <v>5</v>
       </c>
-      <c r="F8" s="225">
+      <c r="F8" s="207">
         <v>5</v>
       </c>
-      <c r="G8" s="225">
+      <c r="G8" s="207">
         <v>6</v>
       </c>
-      <c r="H8" s="225">
+      <c r="H8" s="207">
         <v>7</v>
       </c>
-      <c r="I8" s="225">
+      <c r="I8" s="207">
         <v>5</v>
       </c>
-      <c r="J8" s="225">
+      <c r="J8" s="207">
         <v>6</v>
       </c>
-      <c r="K8" s="225">
+      <c r="K8" s="207">
         <v>5</v>
       </c>
-      <c r="L8" s="225">
+      <c r="L8" s="207">
         <v>5</v>
       </c>
-      <c r="M8" s="225">
+      <c r="M8" s="207">
         <v>5</v>
       </c>
-      <c r="N8" s="222">
-        <f>AVERAGE(C8:M8)</f>
+      <c r="N8" s="204">
+        <f t="shared" si="0"/>
         <v>5.0909090909090908</v>
       </c>
     </row>
@@ -40990,41 +40990,41 @@
       <c r="B9" s="65">
         <v>3</v>
       </c>
-      <c r="C9" s="225">
+      <c r="C9" s="207">
         <v>4</v>
       </c>
-      <c r="D9" s="225">
+      <c r="D9" s="207">
         <v>5</v>
       </c>
-      <c r="E9" s="225">
+      <c r="E9" s="207">
         <v>5</v>
       </c>
-      <c r="F9" s="225">
+      <c r="F9" s="207">
         <v>7</v>
       </c>
-      <c r="G9" s="225">
+      <c r="G9" s="207">
         <v>5</v>
       </c>
-      <c r="H9" s="225">
+      <c r="H9" s="207">
         <v>6</v>
       </c>
-      <c r="I9" s="225">
+      <c r="I9" s="207">
         <v>5</v>
       </c>
-      <c r="J9" s="225">
+      <c r="J9" s="207">
         <v>6</v>
       </c>
-      <c r="K9" s="225">
+      <c r="K9" s="207">
         <v>6</v>
       </c>
-      <c r="L9" s="225">
+      <c r="L9" s="207">
         <v>5</v>
       </c>
-      <c r="M9" s="225">
+      <c r="M9" s="207">
         <v>4</v>
       </c>
-      <c r="N9" s="222">
-        <f>AVERAGE(C9:M9)</f>
+      <c r="N9" s="204">
+        <f t="shared" si="0"/>
         <v>5.2727272727272725</v>
       </c>
     </row>
@@ -41032,44 +41032,44 @@
       <c r="A10" t="s">
         <v>499</v>
       </c>
-      <c r="B10" s="224">
+      <c r="B10" s="206">
         <v>4</v>
       </c>
-      <c r="C10" s="223">
+      <c r="C10" s="205">
         <v>4</v>
       </c>
-      <c r="D10" s="223">
+      <c r="D10" s="205">
         <v>4</v>
       </c>
-      <c r="E10" s="223">
+      <c r="E10" s="205">
         <v>4</v>
       </c>
-      <c r="F10" s="223">
+      <c r="F10" s="205">
         <v>5</v>
       </c>
-      <c r="G10" s="223">
+      <c r="G10" s="205">
         <v>5</v>
       </c>
-      <c r="H10" s="223">
+      <c r="H10" s="205">
         <v>4</v>
       </c>
-      <c r="I10" s="223">
+      <c r="I10" s="205">
         <v>5</v>
       </c>
-      <c r="J10" s="223">
+      <c r="J10" s="205">
         <v>5</v>
       </c>
-      <c r="K10" s="223">
+      <c r="K10" s="205">
         <v>5</v>
       </c>
-      <c r="L10" s="223">
+      <c r="L10" s="205">
         <v>4</v>
       </c>
-      <c r="M10" s="223">
+      <c r="M10" s="205">
         <v>3</v>
       </c>
-      <c r="N10" s="222">
-        <f>AVERAGE(C10:M10)</f>
+      <c r="N10" s="204">
+        <f t="shared" si="0"/>
         <v>4.3636363636363633</v>
       </c>
     </row>
@@ -41077,44 +41077,44 @@
       <c r="A11" t="s">
         <v>498</v>
       </c>
-      <c r="B11" s="224">
+      <c r="B11" s="206">
         <v>5</v>
       </c>
-      <c r="C11" s="223">
+      <c r="C11" s="205">
         <v>5</v>
       </c>
-      <c r="D11" s="223">
+      <c r="D11" s="205">
         <v>5</v>
       </c>
-      <c r="E11" s="223">
+      <c r="E11" s="205">
         <v>4</v>
       </c>
-      <c r="F11" s="223">
+      <c r="F11" s="205">
         <v>5</v>
       </c>
-      <c r="G11" s="223">
+      <c r="G11" s="205">
         <v>7</v>
       </c>
-      <c r="H11" s="223">
+      <c r="H11" s="205">
         <v>6</v>
       </c>
-      <c r="I11" s="223">
+      <c r="I11" s="205">
         <v>6</v>
       </c>
-      <c r="J11" s="223">
+      <c r="J11" s="205">
         <v>5</v>
       </c>
-      <c r="K11" s="223">
+      <c r="K11" s="205">
         <v>5</v>
       </c>
-      <c r="L11" s="223">
+      <c r="L11" s="205">
         <v>4</v>
       </c>
-      <c r="M11" s="223">
+      <c r="M11" s="205">
         <v>5</v>
       </c>
-      <c r="N11" s="222">
-        <f>AVERAGE(C11:M11)</f>
+      <c r="N11" s="204">
+        <f t="shared" si="0"/>
         <v>5.1818181818181817</v>
       </c>
     </row>
@@ -41122,44 +41122,44 @@
       <c r="A12" t="s">
         <v>497</v>
       </c>
-      <c r="B12" s="224">
+      <c r="B12" s="206">
         <v>6</v>
       </c>
-      <c r="C12" s="223">
+      <c r="C12" s="205">
         <v>3</v>
       </c>
-      <c r="D12" s="223">
+      <c r="D12" s="205">
         <v>3</v>
       </c>
-      <c r="E12" s="223">
+      <c r="E12" s="205">
         <v>4</v>
       </c>
-      <c r="F12" s="223">
+      <c r="F12" s="205">
         <v>4</v>
       </c>
-      <c r="G12" s="223">
+      <c r="G12" s="205">
         <v>5</v>
       </c>
-      <c r="H12" s="223">
+      <c r="H12" s="205">
         <v>5</v>
       </c>
-      <c r="I12" s="223">
+      <c r="I12" s="205">
         <v>4</v>
       </c>
-      <c r="J12" s="223">
+      <c r="J12" s="205">
         <v>5</v>
       </c>
-      <c r="K12" s="223">
+      <c r="K12" s="205">
         <v>4</v>
       </c>
-      <c r="L12" s="223">
+      <c r="L12" s="205">
         <v>5</v>
       </c>
-      <c r="M12" s="223">
+      <c r="M12" s="205">
         <v>4</v>
       </c>
-      <c r="N12" s="222">
-        <f>AVERAGE(C12:M12)</f>
+      <c r="N12" s="204">
+        <f t="shared" si="0"/>
         <v>4.1818181818181817</v>
       </c>
     </row>
@@ -41167,44 +41167,44 @@
       <c r="A13" t="s">
         <v>495</v>
       </c>
-      <c r="B13" s="224">
+      <c r="B13" s="206">
         <v>7</v>
       </c>
-      <c r="C13" s="223">
+      <c r="C13" s="205">
         <v>3</v>
       </c>
-      <c r="D13" s="223">
+      <c r="D13" s="205">
         <v>4</v>
       </c>
-      <c r="E13" s="223">
+      <c r="E13" s="205">
         <v>3</v>
       </c>
-      <c r="F13" s="223">
+      <c r="F13" s="205">
         <v>3</v>
       </c>
-      <c r="G13" s="223">
+      <c r="G13" s="205">
         <v>4</v>
       </c>
-      <c r="H13" s="223">
+      <c r="H13" s="205">
         <v>5</v>
       </c>
-      <c r="I13" s="223">
+      <c r="I13" s="205">
         <v>3</v>
       </c>
-      <c r="J13" s="223">
+      <c r="J13" s="205">
         <v>4</v>
       </c>
-      <c r="K13" s="223">
+      <c r="K13" s="205">
         <v>4</v>
       </c>
-      <c r="L13" s="223">
+      <c r="L13" s="205">
         <v>4</v>
       </c>
-      <c r="M13" s="223">
+      <c r="M13" s="205">
         <v>3</v>
       </c>
-      <c r="N13" s="222">
-        <f>AVERAGE(C13:M13)</f>
+      <c r="N13" s="204">
+        <f t="shared" si="0"/>
         <v>3.6363636363636362</v>
       </c>
     </row>
@@ -41212,44 +41212,44 @@
       <c r="A14" t="s">
         <v>496</v>
       </c>
-      <c r="B14" s="224">
+      <c r="B14" s="206">
         <v>8</v>
       </c>
-      <c r="C14" s="223">
+      <c r="C14" s="205">
         <v>3</v>
       </c>
-      <c r="D14" s="223">
+      <c r="D14" s="205">
         <v>4</v>
       </c>
-      <c r="E14" s="223">
+      <c r="E14" s="205">
         <v>5</v>
       </c>
-      <c r="F14" s="223">
+      <c r="F14" s="205">
         <v>4</v>
       </c>
-      <c r="G14" s="223">
+      <c r="G14" s="205">
         <v>5</v>
       </c>
-      <c r="H14" s="223">
+      <c r="H14" s="205">
         <v>6</v>
       </c>
-      <c r="I14" s="223">
+      <c r="I14" s="205">
         <v>4</v>
       </c>
-      <c r="J14" s="223">
+      <c r="J14" s="205">
         <v>3</v>
       </c>
-      <c r="K14" s="223">
+      <c r="K14" s="205">
         <v>4</v>
       </c>
-      <c r="L14" s="223">
+      <c r="L14" s="205">
         <v>3</v>
       </c>
-      <c r="M14" s="223">
+      <c r="M14" s="205">
         <v>4</v>
       </c>
-      <c r="N14" s="222">
-        <f>AVERAGE(C14:M14)</f>
+      <c r="N14" s="204">
+        <f t="shared" si="0"/>
         <v>4.0909090909090908</v>
       </c>
     </row>
@@ -41257,44 +41257,44 @@
       <c r="A15" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="224">
+      <c r="B15" s="206">
         <v>9</v>
       </c>
-      <c r="C15" s="223">
+      <c r="C15" s="205">
         <v>4</v>
       </c>
-      <c r="D15" s="223">
+      <c r="D15" s="205">
         <v>3</v>
       </c>
-      <c r="E15" s="223">
+      <c r="E15" s="205">
         <v>4</v>
       </c>
-      <c r="F15" s="223">
+      <c r="F15" s="205">
         <v>7</v>
       </c>
-      <c r="G15" s="223">
+      <c r="G15" s="205">
         <v>5</v>
       </c>
-      <c r="H15" s="223">
+      <c r="H15" s="205">
         <v>6</v>
       </c>
-      <c r="I15" s="223">
+      <c r="I15" s="205">
         <v>5</v>
       </c>
-      <c r="J15" s="223">
+      <c r="J15" s="205">
         <v>5</v>
       </c>
-      <c r="K15" s="223">
+      <c r="K15" s="205">
         <v>4</v>
       </c>
-      <c r="L15" s="223">
+      <c r="L15" s="205">
         <v>3</v>
       </c>
-      <c r="M15" s="223">
+      <c r="M15" s="205">
         <v>2</v>
       </c>
-      <c r="N15" s="222">
-        <f>AVERAGE(C15:M15)</f>
+      <c r="N15" s="204">
+        <f t="shared" si="0"/>
         <v>4.3636363636363633</v>
       </c>
     </row>
@@ -41302,44 +41302,44 @@
       <c r="A16" t="s">
         <v>495</v>
       </c>
-      <c r="B16" s="224">
+      <c r="B16" s="206">
         <v>10</v>
       </c>
-      <c r="C16" s="223">
+      <c r="C16" s="205">
         <v>2</v>
       </c>
-      <c r="D16" s="223">
+      <c r="D16" s="205">
         <v>3</v>
       </c>
-      <c r="E16" s="223">
+      <c r="E16" s="205">
         <v>4</v>
       </c>
-      <c r="F16" s="223">
+      <c r="F16" s="205">
         <v>5</v>
       </c>
-      <c r="G16" s="223">
+      <c r="G16" s="205">
         <v>4</v>
       </c>
-      <c r="H16" s="223">
+      <c r="H16" s="205">
         <v>5</v>
       </c>
-      <c r="I16" s="223">
+      <c r="I16" s="205">
         <v>4</v>
       </c>
-      <c r="J16" s="223">
+      <c r="J16" s="205">
         <v>5</v>
       </c>
-      <c r="K16" s="223">
+      <c r="K16" s="205">
         <v>5</v>
       </c>
-      <c r="L16" s="223">
+      <c r="L16" s="205">
         <v>3</v>
       </c>
-      <c r="M16" s="223">
+      <c r="M16" s="205">
         <v>3</v>
       </c>
-      <c r="N16" s="222">
-        <f>AVERAGE(C16:M16)</f>
+      <c r="N16" s="204">
+        <f t="shared" si="0"/>
         <v>3.9090909090909092</v>
       </c>
     </row>
@@ -41347,44 +41347,44 @@
       <c r="A17" t="s">
         <v>496</v>
       </c>
-      <c r="B17" s="224">
+      <c r="B17" s="206">
         <v>11</v>
       </c>
-      <c r="C17" s="223">
+      <c r="C17" s="205">
         <v>4</v>
       </c>
-      <c r="D17" s="223">
+      <c r="D17" s="205">
         <v>3</v>
       </c>
-      <c r="E17" s="223">
+      <c r="E17" s="205">
         <v>4</v>
       </c>
-      <c r="F17" s="223">
+      <c r="F17" s="205">
         <v>5</v>
       </c>
-      <c r="G17" s="223">
+      <c r="G17" s="205">
         <v>5</v>
       </c>
-      <c r="H17" s="223">
+      <c r="H17" s="205">
         <v>4</v>
       </c>
-      <c r="I17" s="223">
+      <c r="I17" s="205">
         <v>6</v>
       </c>
-      <c r="J17" s="223">
+      <c r="J17" s="205">
         <v>6</v>
       </c>
-      <c r="K17" s="223">
+      <c r="K17" s="205">
         <v>5</v>
       </c>
-      <c r="L17" s="223">
+      <c r="L17" s="205">
         <v>4</v>
       </c>
-      <c r="M17" s="223">
+      <c r="M17" s="205">
         <v>3</v>
       </c>
-      <c r="N17" s="222">
-        <f>AVERAGE(C17:M17)</f>
+      <c r="N17" s="204">
+        <f t="shared" si="0"/>
         <v>4.4545454545454541</v>
       </c>
     </row>
@@ -41392,44 +41392,44 @@
       <c r="A18" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="224">
+      <c r="B18" s="206">
         <v>12</v>
       </c>
-      <c r="C18" s="223">
+      <c r="C18" s="205">
         <v>3</v>
       </c>
-      <c r="D18" s="223">
+      <c r="D18" s="205">
         <v>3</v>
       </c>
-      <c r="E18" s="223">
+      <c r="E18" s="205">
         <v>3</v>
       </c>
-      <c r="F18" s="223">
+      <c r="F18" s="205">
         <v>4</v>
       </c>
-      <c r="G18" s="223">
+      <c r="G18" s="205">
         <v>4</v>
       </c>
-      <c r="H18" s="223">
+      <c r="H18" s="205">
         <v>5</v>
       </c>
-      <c r="I18" s="223">
+      <c r="I18" s="205">
         <v>5</v>
       </c>
-      <c r="J18" s="223">
+      <c r="J18" s="205">
         <v>4</v>
       </c>
-      <c r="K18" s="223">
+      <c r="K18" s="205">
         <v>5</v>
       </c>
-      <c r="L18" s="223">
+      <c r="L18" s="205">
         <v>4</v>
       </c>
-      <c r="M18" s="223">
+      <c r="M18" s="205">
         <v>4</v>
       </c>
-      <c r="N18" s="222">
-        <f>AVERAGE(C18:M18)</f>
+      <c r="N18" s="204">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -41465,15 +41465,15 @@
       <c r="E1" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="F1" s="235">
+      <c r="F1" s="215">
         <v>45134</v>
       </c>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -41492,75 +41492,75 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>501</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="231" t="s">
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="231"/>
-      <c r="L4" s="231"/>
-      <c r="M4" s="230"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="212"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="228" t="s">
+      <c r="E6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="228" t="s">
+      <c r="F6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="228" t="s">
+      <c r="G6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="228" t="s">
+      <c r="H6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="228" t="s">
+      <c r="I6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="228" t="s">
+      <c r="J6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="228" t="s">
+      <c r="K6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="228" t="s">
+      <c r="L6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="228" t="s">
+      <c r="M6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="227" t="s">
+      <c r="N6" s="209" t="s">
         <v>500</v>
       </c>
     </row>
@@ -41571,41 +41571,41 @@
       <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="226">
+      <c r="C7" s="208">
         <v>2</v>
       </c>
-      <c r="D7" s="226">
+      <c r="D7" s="208">
         <v>3</v>
       </c>
-      <c r="E7" s="226">
+      <c r="E7" s="208">
         <v>3</v>
       </c>
-      <c r="F7" s="226">
+      <c r="F7" s="208">
         <v>5</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="208">
         <v>4</v>
       </c>
-      <c r="H7" s="226">
+      <c r="H7" s="208">
         <v>3</v>
       </c>
-      <c r="I7" s="226">
+      <c r="I7" s="208">
         <v>4</v>
       </c>
-      <c r="J7" s="226">
+      <c r="J7" s="208">
         <v>3</v>
       </c>
-      <c r="K7" s="226">
+      <c r="K7" s="208">
         <v>3</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="208">
         <v>2</v>
       </c>
-      <c r="M7" s="239">
+      <c r="M7" s="219">
         <v>2</v>
       </c>
-      <c r="N7" s="222">
-        <f>AVERAGE(C7:M7)</f>
+      <c r="N7" s="204">
+        <f t="shared" ref="N7:N18" si="0">AVERAGE(C7:M7)</f>
         <v>3.0909090909090908</v>
       </c>
     </row>
@@ -41616,41 +41616,41 @@
       <c r="B8" s="65">
         <v>2</v>
       </c>
-      <c r="C8" s="225">
+      <c r="C8" s="207">
         <v>3</v>
       </c>
-      <c r="D8" s="225">
+      <c r="D8" s="207">
         <v>4</v>
       </c>
-      <c r="E8" s="225">
+      <c r="E8" s="207">
         <v>3</v>
       </c>
-      <c r="F8" s="225">
+      <c r="F8" s="207">
         <v>3</v>
       </c>
-      <c r="G8" s="225">
+      <c r="G8" s="207">
         <v>4</v>
       </c>
-      <c r="H8" s="225">
+      <c r="H8" s="207">
         <v>3</v>
       </c>
-      <c r="I8" s="225">
+      <c r="I8" s="207">
         <v>3</v>
       </c>
-      <c r="J8" s="225">
+      <c r="J8" s="207">
         <v>4</v>
       </c>
-      <c r="K8" s="225">
+      <c r="K8" s="207">
         <v>5</v>
       </c>
-      <c r="L8" s="225">
+      <c r="L8" s="207">
         <v>4</v>
       </c>
-      <c r="M8" s="237">
+      <c r="M8" s="217">
         <v>4</v>
       </c>
-      <c r="N8" s="222">
-        <f>AVERAGE(C8:M8)</f>
+      <c r="N8" s="204">
+        <f t="shared" si="0"/>
         <v>3.6363636363636362</v>
       </c>
     </row>
@@ -41661,41 +41661,41 @@
       <c r="B9" s="65">
         <v>3</v>
       </c>
-      <c r="C9" s="225">
+      <c r="C9" s="207">
         <v>3</v>
       </c>
-      <c r="D9" s="225">
+      <c r="D9" s="207">
         <v>3</v>
       </c>
-      <c r="E9" s="225">
+      <c r="E9" s="207">
         <v>5</v>
       </c>
-      <c r="F9" s="238">
+      <c r="F9" s="218">
         <v>4</v>
       </c>
-      <c r="G9" s="225">
+      <c r="G9" s="207">
         <v>4</v>
       </c>
-      <c r="H9" s="225">
+      <c r="H9" s="207">
         <v>4</v>
       </c>
-      <c r="I9" s="225">
+      <c r="I9" s="207">
         <v>4</v>
       </c>
-      <c r="J9" s="225">
+      <c r="J9" s="207">
         <v>4</v>
       </c>
-      <c r="K9" s="225">
+      <c r="K9" s="207">
         <v>3</v>
       </c>
-      <c r="L9" s="225">
+      <c r="L9" s="207">
         <v>3</v>
       </c>
-      <c r="M9" s="237">
+      <c r="M9" s="217">
         <v>3</v>
       </c>
-      <c r="N9" s="222">
-        <f>AVERAGE(C9:M9)</f>
+      <c r="N9" s="204">
+        <f t="shared" si="0"/>
         <v>3.6363636363636362</v>
       </c>
     </row>
@@ -41703,44 +41703,44 @@
       <c r="A10" t="s">
         <v>499</v>
       </c>
-      <c r="B10" s="224">
+      <c r="B10" s="206">
         <v>4</v>
       </c>
-      <c r="C10" s="225">
+      <c r="C10" s="207">
         <v>3</v>
       </c>
-      <c r="D10" s="225">
+      <c r="D10" s="207">
         <v>2</v>
       </c>
-      <c r="E10" s="225">
+      <c r="E10" s="207">
         <v>3</v>
       </c>
-      <c r="F10" s="225">
+      <c r="F10" s="207">
         <v>1</v>
       </c>
-      <c r="G10" s="225">
+      <c r="G10" s="207">
         <v>2</v>
       </c>
-      <c r="H10" s="225">
+      <c r="H10" s="207">
         <v>3</v>
       </c>
-      <c r="I10" s="225">
+      <c r="I10" s="207">
         <v>3</v>
       </c>
-      <c r="J10" s="225">
+      <c r="J10" s="207">
         <v>3</v>
       </c>
-      <c r="K10" s="225">
+      <c r="K10" s="207">
         <v>3</v>
       </c>
-      <c r="L10" s="225">
+      <c r="L10" s="207">
         <v>3</v>
       </c>
-      <c r="M10" s="237">
+      <c r="M10" s="217">
         <v>2</v>
       </c>
-      <c r="N10" s="222">
-        <f>AVERAGE(C10:M10)</f>
+      <c r="N10" s="204">
+        <f t="shared" si="0"/>
         <v>2.5454545454545454</v>
       </c>
     </row>
@@ -41748,44 +41748,44 @@
       <c r="A11" t="s">
         <v>498</v>
       </c>
-      <c r="B11" s="224">
+      <c r="B11" s="206">
         <v>5</v>
       </c>
-      <c r="C11" s="225">
+      <c r="C11" s="207">
         <v>3</v>
       </c>
-      <c r="D11" s="225">
+      <c r="D11" s="207">
         <v>4</v>
       </c>
-      <c r="E11" s="225">
+      <c r="E11" s="207">
         <v>5</v>
       </c>
-      <c r="F11" s="225">
+      <c r="F11" s="207">
         <v>4</v>
       </c>
-      <c r="G11" s="225">
+      <c r="G11" s="207">
         <v>3</v>
       </c>
-      <c r="H11" s="225">
+      <c r="H11" s="207">
         <v>4</v>
       </c>
-      <c r="I11" s="225">
+      <c r="I11" s="207">
         <v>4</v>
       </c>
-      <c r="J11" s="225">
+      <c r="J11" s="207">
         <v>5</v>
       </c>
-      <c r="K11" s="225">
+      <c r="K11" s="207">
         <v>5</v>
       </c>
-      <c r="L11" s="225">
+      <c r="L11" s="207">
         <v>5</v>
       </c>
-      <c r="M11" s="237">
+      <c r="M11" s="217">
         <v>3</v>
       </c>
-      <c r="N11" s="222">
-        <f>AVERAGE(C11:M11)</f>
+      <c r="N11" s="204">
+        <f t="shared" si="0"/>
         <v>4.0909090909090908</v>
       </c>
     </row>
@@ -41793,44 +41793,44 @@
       <c r="A12" t="s">
         <v>497</v>
       </c>
-      <c r="B12" s="224">
+      <c r="B12" s="206">
         <v>6</v>
       </c>
-      <c r="C12" s="225">
+      <c r="C12" s="207">
         <v>3</v>
       </c>
-      <c r="D12" s="225">
+      <c r="D12" s="207">
         <v>3</v>
       </c>
-      <c r="E12" s="225">
+      <c r="E12" s="207">
         <v>2</v>
       </c>
-      <c r="F12" s="225">
+      <c r="F12" s="207">
         <v>3</v>
       </c>
-      <c r="G12" s="225">
+      <c r="G12" s="207">
         <v>3</v>
       </c>
-      <c r="H12" s="225">
+      <c r="H12" s="207">
         <v>3</v>
       </c>
-      <c r="I12" s="225">
+      <c r="I12" s="207">
         <v>2</v>
       </c>
-      <c r="J12" s="225">
+      <c r="J12" s="207">
         <v>3</v>
       </c>
-      <c r="K12" s="225">
+      <c r="K12" s="207">
         <v>3</v>
       </c>
-      <c r="L12" s="225">
+      <c r="L12" s="207">
         <v>2</v>
       </c>
-      <c r="M12" s="237">
+      <c r="M12" s="217">
         <v>2</v>
       </c>
-      <c r="N12" s="222">
-        <f>AVERAGE(C12:M12)</f>
+      <c r="N12" s="204">
+        <f t="shared" si="0"/>
         <v>2.6363636363636362</v>
       </c>
     </row>
@@ -41838,44 +41838,44 @@
       <c r="A13" t="s">
         <v>495</v>
       </c>
-      <c r="B13" s="224">
+      <c r="B13" s="206">
         <v>7</v>
       </c>
-      <c r="C13" s="225">
+      <c r="C13" s="207">
         <v>2</v>
       </c>
-      <c r="D13" s="225">
+      <c r="D13" s="207">
         <v>2</v>
       </c>
-      <c r="E13" s="225">
+      <c r="E13" s="207">
         <v>2</v>
       </c>
-      <c r="F13" s="225">
+      <c r="F13" s="207">
         <v>3</v>
       </c>
-      <c r="G13" s="225">
+      <c r="G13" s="207">
         <v>3</v>
       </c>
-      <c r="H13" s="225">
+      <c r="H13" s="207">
         <v>2</v>
       </c>
-      <c r="I13" s="225">
+      <c r="I13" s="207">
         <v>2</v>
       </c>
-      <c r="J13" s="225">
+      <c r="J13" s="207">
         <v>1</v>
       </c>
-      <c r="K13" s="225">
+      <c r="K13" s="207">
         <v>2</v>
       </c>
-      <c r="L13" s="225">
+      <c r="L13" s="207">
         <v>2</v>
       </c>
-      <c r="M13" s="237">
+      <c r="M13" s="217">
         <v>2</v>
       </c>
-      <c r="N13" s="222">
-        <f>AVERAGE(C13:M13)</f>
+      <c r="N13" s="204">
+        <f t="shared" si="0"/>
         <v>2.0909090909090908</v>
       </c>
     </row>
@@ -41883,44 +41883,44 @@
       <c r="A14" t="s">
         <v>496</v>
       </c>
-      <c r="B14" s="224">
+      <c r="B14" s="206">
         <v>8</v>
       </c>
-      <c r="C14" s="225">
+      <c r="C14" s="207">
         <v>2</v>
       </c>
-      <c r="D14" s="225">
+      <c r="D14" s="207">
         <v>4</v>
       </c>
-      <c r="E14" s="225">
+      <c r="E14" s="207">
         <v>4</v>
       </c>
-      <c r="F14" s="225">
+      <c r="F14" s="207">
         <v>3</v>
       </c>
-      <c r="G14" s="225">
+      <c r="G14" s="207">
         <v>3</v>
       </c>
-      <c r="H14" s="225">
+      <c r="H14" s="207">
         <v>4</v>
       </c>
-      <c r="I14" s="225">
+      <c r="I14" s="207">
         <v>2</v>
       </c>
-      <c r="J14" s="225">
+      <c r="J14" s="207">
         <v>2</v>
       </c>
-      <c r="K14" s="225">
+      <c r="K14" s="207">
         <v>3</v>
       </c>
-      <c r="L14" s="225">
+      <c r="L14" s="207">
         <v>2</v>
       </c>
-      <c r="M14" s="237">
+      <c r="M14" s="217">
         <v>2</v>
       </c>
-      <c r="N14" s="222">
-        <f>AVERAGE(C14:M14)</f>
+      <c r="N14" s="204">
+        <f t="shared" si="0"/>
         <v>2.8181818181818183</v>
       </c>
     </row>
@@ -41928,44 +41928,44 @@
       <c r="A15" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="224">
+      <c r="B15" s="206">
         <v>9</v>
       </c>
-      <c r="C15" s="225">
+      <c r="C15" s="207">
         <v>2</v>
       </c>
-      <c r="D15" s="225">
+      <c r="D15" s="207">
         <v>3</v>
       </c>
-      <c r="E15" s="225">
+      <c r="E15" s="207">
         <v>3</v>
       </c>
-      <c r="F15" s="225">
+      <c r="F15" s="207">
         <v>4</v>
       </c>
-      <c r="G15" s="225">
+      <c r="G15" s="207">
         <v>3</v>
       </c>
-      <c r="H15" s="225">
+      <c r="H15" s="207">
         <v>2</v>
       </c>
-      <c r="I15" s="225">
+      <c r="I15" s="207">
         <v>4</v>
       </c>
-      <c r="J15" s="225">
+      <c r="J15" s="207">
         <v>2</v>
       </c>
-      <c r="K15" s="225">
+      <c r="K15" s="207">
         <v>3</v>
       </c>
-      <c r="L15" s="225">
+      <c r="L15" s="207">
         <v>4</v>
       </c>
-      <c r="M15" s="237">
+      <c r="M15" s="217">
         <v>3</v>
       </c>
-      <c r="N15" s="222">
-        <f>AVERAGE(C15:M15)</f>
+      <c r="N15" s="204">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -41973,44 +41973,44 @@
       <c r="A16" t="s">
         <v>495</v>
       </c>
-      <c r="B16" s="224">
+      <c r="B16" s="206">
         <v>10</v>
       </c>
-      <c r="C16" s="225">
+      <c r="C16" s="207">
         <v>1</v>
       </c>
-      <c r="D16" s="225">
+      <c r="D16" s="207">
         <v>2</v>
       </c>
-      <c r="E16" s="225">
+      <c r="E16" s="207">
         <v>2</v>
       </c>
-      <c r="F16" s="225">
+      <c r="F16" s="207">
         <v>3</v>
       </c>
-      <c r="G16" s="225">
+      <c r="G16" s="207">
         <v>3</v>
       </c>
-      <c r="H16" s="225">
+      <c r="H16" s="207">
         <v>3</v>
       </c>
-      <c r="I16" s="225">
+      <c r="I16" s="207">
         <v>2</v>
       </c>
-      <c r="J16" s="225">
+      <c r="J16" s="207">
         <v>2</v>
       </c>
-      <c r="K16" s="225">
+      <c r="K16" s="207">
         <v>3</v>
       </c>
-      <c r="L16" s="225">
+      <c r="L16" s="207">
         <v>2</v>
       </c>
-      <c r="M16" s="237">
+      <c r="M16" s="217">
         <v>2</v>
       </c>
-      <c r="N16" s="222">
-        <f>AVERAGE(C16:M16)</f>
+      <c r="N16" s="204">
+        <f t="shared" si="0"/>
         <v>2.2727272727272729</v>
       </c>
     </row>
@@ -42018,44 +42018,44 @@
       <c r="A17" t="s">
         <v>496</v>
       </c>
-      <c r="B17" s="224">
+      <c r="B17" s="206">
         <v>11</v>
       </c>
-      <c r="C17" s="225">
+      <c r="C17" s="207">
         <v>2</v>
       </c>
-      <c r="D17" s="225">
+      <c r="D17" s="207">
         <v>3</v>
       </c>
-      <c r="E17" s="225">
+      <c r="E17" s="207">
         <v>3</v>
       </c>
-      <c r="F17" s="225">
+      <c r="F17" s="207">
         <v>2</v>
       </c>
-      <c r="G17" s="225">
+      <c r="G17" s="207">
         <v>4</v>
       </c>
-      <c r="H17" s="225">
+      <c r="H17" s="207">
         <v>3</v>
       </c>
-      <c r="I17" s="225">
+      <c r="I17" s="207">
         <v>3</v>
       </c>
-      <c r="J17" s="225">
+      <c r="J17" s="207">
         <v>2</v>
       </c>
-      <c r="K17" s="225">
+      <c r="K17" s="207">
         <v>4</v>
       </c>
-      <c r="L17" s="225">
+      <c r="L17" s="207">
         <v>2</v>
       </c>
-      <c r="M17" s="237">
+      <c r="M17" s="217">
         <v>2</v>
       </c>
-      <c r="N17" s="222">
-        <f>AVERAGE(C17:M17)</f>
+      <c r="N17" s="204">
+        <f t="shared" si="0"/>
         <v>2.7272727272727271</v>
       </c>
     </row>
@@ -42063,44 +42063,44 @@
       <c r="A18" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="224">
+      <c r="B18" s="206">
         <v>12</v>
       </c>
-      <c r="C18" s="223">
+      <c r="C18" s="205">
         <v>2</v>
       </c>
-      <c r="D18" s="223">
+      <c r="D18" s="205">
         <v>2</v>
       </c>
-      <c r="E18" s="223">
+      <c r="E18" s="205">
         <v>1</v>
       </c>
-      <c r="F18" s="223">
+      <c r="F18" s="205">
         <v>3</v>
       </c>
-      <c r="G18" s="223">
+      <c r="G18" s="205">
         <v>2</v>
       </c>
-      <c r="H18" s="223">
+      <c r="H18" s="205">
         <v>2</v>
       </c>
-      <c r="I18" s="223">
+      <c r="I18" s="205">
         <v>3</v>
       </c>
-      <c r="J18" s="223">
+      <c r="J18" s="205">
         <v>2</v>
       </c>
-      <c r="K18" s="223">
+      <c r="K18" s="205">
         <v>3</v>
       </c>
-      <c r="L18" s="223">
+      <c r="L18" s="205">
         <v>2</v>
       </c>
-      <c r="M18" s="236">
+      <c r="M18" s="216">
         <v>2</v>
       </c>
-      <c r="N18" s="222">
-        <f>AVERAGE(C18:M18)</f>
+      <c r="N18" s="204">
+        <f t="shared" si="0"/>
         <v>2.1818181818181817</v>
       </c>
     </row>
@@ -42136,15 +42136,15 @@
       <c r="E1" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="F1" s="235">
+      <c r="F1" s="215">
         <v>45141</v>
       </c>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -42163,75 +42163,75 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>501</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="231" t="s">
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="231"/>
-      <c r="L4" s="231"/>
-      <c r="M4" s="230"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="212"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="228" t="s">
+      <c r="E6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="228" t="s">
+      <c r="F6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="228" t="s">
+      <c r="G6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="228" t="s">
+      <c r="H6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="228" t="s">
+      <c r="I6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="228" t="s">
+      <c r="J6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="228" t="s">
+      <c r="K6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="228" t="s">
+      <c r="L6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="228" t="s">
+      <c r="M6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="227" t="s">
+      <c r="N6" s="209" t="s">
         <v>500</v>
       </c>
     </row>
@@ -42242,41 +42242,41 @@
       <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="226">
+      <c r="C7" s="208">
         <v>1</v>
       </c>
-      <c r="D7" s="226">
+      <c r="D7" s="208">
         <v>1</v>
       </c>
-      <c r="E7" s="226">
+      <c r="E7" s="208">
         <v>2</v>
       </c>
-      <c r="F7" s="226">
+      <c r="F7" s="208">
         <v>4</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="208">
         <v>3</v>
       </c>
-      <c r="H7" s="226">
+      <c r="H7" s="208">
         <v>3</v>
       </c>
-      <c r="I7" s="226">
+      <c r="I7" s="208">
         <v>3</v>
       </c>
-      <c r="J7" s="226">
+      <c r="J7" s="208">
         <v>3</v>
       </c>
-      <c r="K7" s="226">
+      <c r="K7" s="208">
         <v>2</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="208">
         <v>2</v>
       </c>
-      <c r="M7" s="226">
+      <c r="M7" s="208">
         <v>2</v>
       </c>
-      <c r="N7" s="222">
-        <f>AVERAGE(C7:M7)</f>
+      <c r="N7" s="204">
+        <f t="shared" ref="N7:N18" si="0">AVERAGE(C7:M7)</f>
         <v>2.3636363636363638</v>
       </c>
     </row>
@@ -42287,41 +42287,41 @@
       <c r="B8" s="65">
         <v>2</v>
       </c>
-      <c r="C8" s="225">
+      <c r="C8" s="207">
         <v>2</v>
       </c>
-      <c r="D8" s="225">
+      <c r="D8" s="207">
         <v>3</v>
       </c>
-      <c r="E8" s="225">
+      <c r="E8" s="207">
         <v>3</v>
       </c>
-      <c r="F8" s="225">
+      <c r="F8" s="207">
         <v>4</v>
       </c>
-      <c r="G8" s="225">
+      <c r="G8" s="207">
         <v>3</v>
       </c>
-      <c r="H8" s="225">
+      <c r="H8" s="207">
         <v>4</v>
       </c>
-      <c r="I8" s="225">
+      <c r="I8" s="207">
         <v>4</v>
       </c>
-      <c r="J8" s="225">
+      <c r="J8" s="207">
         <v>3</v>
       </c>
-      <c r="K8" s="225">
+      <c r="K8" s="207">
         <v>3</v>
       </c>
-      <c r="L8" s="225">
+      <c r="L8" s="207">
         <v>3</v>
       </c>
-      <c r="M8" s="225">
+      <c r="M8" s="207">
         <v>2</v>
       </c>
-      <c r="N8" s="222">
-        <f>AVERAGE(C8:M8)</f>
+      <c r="N8" s="204">
+        <f t="shared" si="0"/>
         <v>3.0909090909090908</v>
       </c>
     </row>
@@ -42332,41 +42332,41 @@
       <c r="B9" s="65">
         <v>3</v>
       </c>
-      <c r="C9" s="225">
+      <c r="C9" s="207">
         <v>2</v>
       </c>
-      <c r="D9" s="225">
+      <c r="D9" s="207">
         <v>2</v>
       </c>
-      <c r="E9" s="225">
+      <c r="E9" s="207">
         <v>3</v>
       </c>
-      <c r="F9" s="225">
+      <c r="F9" s="207">
         <v>3</v>
       </c>
-      <c r="G9" s="225">
+      <c r="G9" s="207">
         <v>4</v>
       </c>
-      <c r="H9" s="225">
+      <c r="H9" s="207">
         <v>5</v>
       </c>
-      <c r="I9" s="225">
+      <c r="I9" s="207">
         <v>3</v>
       </c>
-      <c r="J9" s="225">
+      <c r="J9" s="207">
         <v>4</v>
       </c>
-      <c r="K9" s="225">
+      <c r="K9" s="207">
         <v>3</v>
       </c>
-      <c r="L9" s="225">
+      <c r="L9" s="207">
         <v>3</v>
       </c>
-      <c r="M9" s="225">
+      <c r="M9" s="207">
         <v>3</v>
       </c>
-      <c r="N9" s="222">
-        <f>AVERAGE(C9:M9)</f>
+      <c r="N9" s="204">
+        <f t="shared" si="0"/>
         <v>3.1818181818181817</v>
       </c>
     </row>
@@ -42374,44 +42374,44 @@
       <c r="A10" t="s">
         <v>499</v>
       </c>
-      <c r="B10" s="224">
+      <c r="B10" s="206">
         <v>4</v>
       </c>
-      <c r="C10" s="223">
+      <c r="C10" s="205">
         <v>1</v>
       </c>
-      <c r="D10" s="223">
+      <c r="D10" s="205">
         <v>2</v>
       </c>
-      <c r="E10" s="223">
+      <c r="E10" s="205">
         <v>2</v>
       </c>
-      <c r="F10" s="223">
+      <c r="F10" s="205">
         <v>2</v>
       </c>
-      <c r="G10" s="223">
+      <c r="G10" s="205">
         <v>1</v>
       </c>
-      <c r="H10" s="223">
+      <c r="H10" s="205">
         <v>2</v>
       </c>
-      <c r="I10" s="223">
+      <c r="I10" s="205">
         <v>2</v>
       </c>
-      <c r="J10" s="223">
+      <c r="J10" s="205">
         <v>4</v>
       </c>
-      <c r="K10" s="223">
+      <c r="K10" s="205">
         <v>3</v>
       </c>
-      <c r="L10" s="223">
+      <c r="L10" s="205">
         <v>2</v>
       </c>
-      <c r="M10" s="223">
+      <c r="M10" s="205">
         <v>2</v>
       </c>
-      <c r="N10" s="222">
-        <f>AVERAGE(C10:M10)</f>
+      <c r="N10" s="204">
+        <f t="shared" si="0"/>
         <v>2.0909090909090908</v>
       </c>
     </row>
@@ -42419,44 +42419,44 @@
       <c r="A11" t="s">
         <v>498</v>
       </c>
-      <c r="B11" s="224">
+      <c r="B11" s="206">
         <v>5</v>
       </c>
-      <c r="C11" s="223">
+      <c r="C11" s="205">
         <v>1</v>
       </c>
-      <c r="D11" s="223">
+      <c r="D11" s="205">
         <v>1</v>
       </c>
-      <c r="E11" s="223">
+      <c r="E11" s="205">
         <v>3</v>
       </c>
-      <c r="F11" s="223">
+      <c r="F11" s="205">
         <v>4</v>
       </c>
-      <c r="G11" s="223">
+      <c r="G11" s="205">
         <v>5</v>
       </c>
-      <c r="H11" s="223">
+      <c r="H11" s="205">
         <v>5</v>
       </c>
-      <c r="I11" s="223">
+      <c r="I11" s="205">
         <v>4</v>
       </c>
-      <c r="J11" s="223">
+      <c r="J11" s="205">
         <v>4</v>
       </c>
-      <c r="K11" s="223">
+      <c r="K11" s="205">
         <v>3</v>
       </c>
-      <c r="L11" s="223">
+      <c r="L11" s="205">
         <v>3</v>
       </c>
-      <c r="M11" s="223">
+      <c r="M11" s="205">
         <v>3</v>
       </c>
-      <c r="N11" s="222">
-        <f>AVERAGE(C11:M11)</f>
+      <c r="N11" s="204">
+        <f t="shared" si="0"/>
         <v>3.2727272727272729</v>
       </c>
     </row>
@@ -42464,44 +42464,44 @@
       <c r="A12" t="s">
         <v>497</v>
       </c>
-      <c r="B12" s="224">
+      <c r="B12" s="206">
         <v>6</v>
       </c>
-      <c r="C12" s="223">
+      <c r="C12" s="205">
         <v>1</v>
       </c>
-      <c r="D12" s="223">
+      <c r="D12" s="205">
         <v>1</v>
       </c>
-      <c r="E12" s="223">
+      <c r="E12" s="205">
         <v>1</v>
       </c>
-      <c r="F12" s="223">
+      <c r="F12" s="205">
         <v>2</v>
       </c>
-      <c r="G12" s="223">
+      <c r="G12" s="205">
         <v>3</v>
       </c>
-      <c r="H12" s="223">
+      <c r="H12" s="205">
         <v>4</v>
       </c>
-      <c r="I12" s="223">
+      <c r="I12" s="205">
         <v>2</v>
       </c>
-      <c r="J12" s="223">
+      <c r="J12" s="205">
         <v>3</v>
       </c>
-      <c r="K12" s="223">
+      <c r="K12" s="205">
         <v>2</v>
       </c>
-      <c r="L12" s="223">
+      <c r="L12" s="205">
         <v>2</v>
       </c>
-      <c r="M12" s="223">
+      <c r="M12" s="205">
         <v>1</v>
       </c>
-      <c r="N12" s="222">
-        <f>AVERAGE(C12:M12)</f>
+      <c r="N12" s="204">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -42509,44 +42509,44 @@
       <c r="A13" t="s">
         <v>495</v>
       </c>
-      <c r="B13" s="224">
+      <c r="B13" s="206">
         <v>7</v>
       </c>
-      <c r="C13" s="223">
+      <c r="C13" s="205">
         <v>1</v>
       </c>
-      <c r="D13" s="223">
+      <c r="D13" s="205">
         <v>1</v>
       </c>
-      <c r="E13" s="223">
+      <c r="E13" s="205">
         <v>1</v>
       </c>
-      <c r="F13" s="223">
+      <c r="F13" s="205">
         <v>1</v>
       </c>
-      <c r="G13" s="223">
+      <c r="G13" s="205">
         <v>1</v>
       </c>
-      <c r="H13" s="223">
+      <c r="H13" s="205">
         <v>2</v>
       </c>
-      <c r="I13" s="223">
+      <c r="I13" s="205">
         <v>2</v>
       </c>
-      <c r="J13" s="223">
+      <c r="J13" s="205">
         <v>2</v>
       </c>
-      <c r="K13" s="223">
+      <c r="K13" s="205">
         <v>2</v>
       </c>
-      <c r="L13" s="223">
+      <c r="L13" s="205">
         <v>1</v>
       </c>
-      <c r="M13" s="223">
+      <c r="M13" s="205">
         <v>1</v>
       </c>
-      <c r="N13" s="222">
-        <f>AVERAGE(C13:M13)</f>
+      <c r="N13" s="204">
+        <f t="shared" si="0"/>
         <v>1.3636363636363635</v>
       </c>
     </row>
@@ -42554,44 +42554,44 @@
       <c r="A14" t="s">
         <v>496</v>
       </c>
-      <c r="B14" s="224">
+      <c r="B14" s="206">
         <v>8</v>
       </c>
-      <c r="C14" s="223">
+      <c r="C14" s="205">
         <v>1</v>
       </c>
-      <c r="D14" s="223">
+      <c r="D14" s="205">
         <v>2</v>
       </c>
-      <c r="E14" s="223">
+      <c r="E14" s="205">
         <v>2</v>
       </c>
-      <c r="F14" s="223">
+      <c r="F14" s="205">
         <v>3</v>
       </c>
-      <c r="G14" s="223">
+      <c r="G14" s="205">
         <v>3</v>
       </c>
-      <c r="H14" s="223">
+      <c r="H14" s="205">
         <v>4</v>
       </c>
-      <c r="I14" s="223">
+      <c r="I14" s="205">
         <v>2</v>
       </c>
-      <c r="J14" s="223">
+      <c r="J14" s="205">
         <v>3</v>
       </c>
-      <c r="K14" s="223">
+      <c r="K14" s="205">
         <v>3</v>
       </c>
-      <c r="L14" s="223">
+      <c r="L14" s="205">
         <v>1</v>
       </c>
-      <c r="M14" s="223">
+      <c r="M14" s="205">
         <v>1</v>
       </c>
-      <c r="N14" s="222">
-        <f>AVERAGE(C14:M14)</f>
+      <c r="N14" s="204">
+        <f t="shared" si="0"/>
         <v>2.2727272727272729</v>
       </c>
     </row>
@@ -42599,44 +42599,44 @@
       <c r="A15" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="224">
+      <c r="B15" s="206">
         <v>9</v>
       </c>
-      <c r="C15" s="223">
+      <c r="C15" s="205">
         <v>1</v>
       </c>
-      <c r="D15" s="223">
+      <c r="D15" s="205">
         <v>2</v>
       </c>
-      <c r="E15" s="223">
+      <c r="E15" s="205">
         <v>1</v>
       </c>
-      <c r="F15" s="223">
+      <c r="F15" s="205">
         <v>1</v>
       </c>
-      <c r="G15" s="223">
+      <c r="G15" s="205">
         <v>3</v>
       </c>
-      <c r="H15" s="223">
+      <c r="H15" s="205">
         <v>3</v>
       </c>
-      <c r="I15" s="223">
+      <c r="I15" s="205">
         <v>3</v>
       </c>
-      <c r="J15" s="223">
+      <c r="J15" s="205">
         <v>3</v>
       </c>
-      <c r="K15" s="223">
+      <c r="K15" s="205">
         <v>2</v>
       </c>
-      <c r="L15" s="223">
+      <c r="L15" s="205">
         <v>3</v>
       </c>
-      <c r="M15" s="223">
+      <c r="M15" s="205">
         <v>1</v>
       </c>
-      <c r="N15" s="222">
-        <f>AVERAGE(C15:M15)</f>
+      <c r="N15" s="204">
+        <f t="shared" si="0"/>
         <v>2.0909090909090908</v>
       </c>
     </row>
@@ -42644,44 +42644,44 @@
       <c r="A16" t="s">
         <v>495</v>
       </c>
-      <c r="B16" s="224">
+      <c r="B16" s="206">
         <v>10</v>
       </c>
-      <c r="C16" s="223">
+      <c r="C16" s="205">
         <v>1</v>
       </c>
-      <c r="D16" s="223">
+      <c r="D16" s="205">
         <v>2</v>
       </c>
-      <c r="E16" s="223">
+      <c r="E16" s="205">
         <v>2</v>
       </c>
-      <c r="F16" s="223">
+      <c r="F16" s="205">
         <v>2</v>
       </c>
-      <c r="G16" s="223">
+      <c r="G16" s="205">
         <v>2</v>
       </c>
-      <c r="H16" s="223">
+      <c r="H16" s="205">
         <v>3</v>
       </c>
-      <c r="I16" s="223">
+      <c r="I16" s="205">
         <v>2</v>
       </c>
-      <c r="J16" s="223">
+      <c r="J16" s="205">
         <v>2</v>
       </c>
-      <c r="K16" s="223">
+      <c r="K16" s="205">
         <v>1</v>
       </c>
-      <c r="L16" s="223">
+      <c r="L16" s="205">
         <v>2</v>
       </c>
-      <c r="M16" s="223">
+      <c r="M16" s="205">
         <v>1</v>
       </c>
-      <c r="N16" s="222">
-        <f>AVERAGE(C16:M16)</f>
+      <c r="N16" s="204">
+        <f t="shared" si="0"/>
         <v>1.8181818181818181</v>
       </c>
     </row>
@@ -42689,44 +42689,44 @@
       <c r="A17" t="s">
         <v>496</v>
       </c>
-      <c r="B17" s="224">
+      <c r="B17" s="206">
         <v>11</v>
       </c>
-      <c r="C17" s="223">
+      <c r="C17" s="205">
         <v>1</v>
       </c>
-      <c r="D17" s="223">
+      <c r="D17" s="205">
         <v>3</v>
       </c>
-      <c r="E17" s="223">
+      <c r="E17" s="205">
         <v>2</v>
       </c>
-      <c r="F17" s="223">
+      <c r="F17" s="205">
         <v>2</v>
       </c>
-      <c r="G17" s="223">
+      <c r="G17" s="205">
         <v>2</v>
       </c>
-      <c r="H17" s="223">
+      <c r="H17" s="205">
         <v>3</v>
       </c>
-      <c r="I17" s="223">
+      <c r="I17" s="205">
         <v>2</v>
       </c>
-      <c r="J17" s="223">
+      <c r="J17" s="205">
         <v>3</v>
       </c>
-      <c r="K17" s="223">
+      <c r="K17" s="205">
         <v>2</v>
       </c>
-      <c r="L17" s="223">
+      <c r="L17" s="205">
         <v>1</v>
       </c>
-      <c r="M17" s="223">
+      <c r="M17" s="205">
         <v>1</v>
       </c>
-      <c r="N17" s="222">
-        <f>AVERAGE(C17:M17)</f>
+      <c r="N17" s="204">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -42734,44 +42734,44 @@
       <c r="A18" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="224">
+      <c r="B18" s="206">
         <v>12</v>
       </c>
-      <c r="C18" s="223">
+      <c r="C18" s="205">
         <v>1</v>
       </c>
-      <c r="D18" s="223">
+      <c r="D18" s="205">
         <v>1</v>
       </c>
-      <c r="E18" s="223">
+      <c r="E18" s="205">
         <v>2</v>
       </c>
-      <c r="F18" s="223">
+      <c r="F18" s="205">
         <v>1</v>
       </c>
-      <c r="G18" s="223">
+      <c r="G18" s="205">
         <v>2</v>
       </c>
-      <c r="H18" s="223">
+      <c r="H18" s="205">
         <v>2</v>
       </c>
-      <c r="I18" s="223">
+      <c r="I18" s="205">
         <v>1</v>
       </c>
-      <c r="J18" s="223">
+      <c r="J18" s="205">
         <v>2</v>
       </c>
-      <c r="K18" s="223">
+      <c r="K18" s="205">
         <v>3</v>
       </c>
-      <c r="L18" s="223">
+      <c r="L18" s="205">
         <v>2</v>
       </c>
-      <c r="M18" s="223">
+      <c r="M18" s="205">
         <v>1</v>
       </c>
-      <c r="N18" s="222">
-        <f>AVERAGE(C18:M18)</f>
+      <c r="N18" s="204">
+        <f t="shared" si="0"/>
         <v>1.6363636363636365</v>
       </c>
     </row>
@@ -49158,12 +49158,12 @@
       <c r="F1" s="14">
         <v>45162</v>
       </c>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -49182,75 +49182,75 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>501</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="231" t="s">
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="231"/>
-      <c r="L4" s="231"/>
-      <c r="M4" s="230"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="212"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="228" t="s">
+      <c r="E6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="228" t="s">
+      <c r="F6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="228" t="s">
+      <c r="G6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="228" t="s">
+      <c r="H6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="228" t="s">
+      <c r="I6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="228" t="s">
+      <c r="J6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="228" t="s">
+      <c r="K6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="228" t="s">
+      <c r="L6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="228" t="s">
+      <c r="M6" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="227" t="s">
+      <c r="N6" s="209" t="s">
         <v>500</v>
       </c>
     </row>
@@ -49261,41 +49261,41 @@
       <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="226">
+      <c r="C7" s="208">
         <v>0</v>
       </c>
-      <c r="D7" s="226">
+      <c r="D7" s="208">
         <v>1</v>
       </c>
-      <c r="E7" s="226">
+      <c r="E7" s="208">
         <v>0</v>
       </c>
-      <c r="F7" s="226">
+      <c r="F7" s="208">
         <v>1</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="208">
         <v>1</v>
       </c>
-      <c r="H7" s="226">
+      <c r="H7" s="208">
         <v>2</v>
       </c>
-      <c r="I7" s="226">
+      <c r="I7" s="208">
         <v>2</v>
       </c>
-      <c r="J7" s="226">
+      <c r="J7" s="208">
         <v>2</v>
       </c>
-      <c r="K7" s="226">
+      <c r="K7" s="208">
         <v>2</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="208">
         <v>1</v>
       </c>
-      <c r="M7" s="226">
+      <c r="M7" s="208">
         <v>0</v>
       </c>
-      <c r="N7" s="222">
-        <f>AVERAGE(C7:M7)</f>
+      <c r="N7" s="204">
+        <f t="shared" ref="N7:N18" si="0">AVERAGE(C7:M7)</f>
         <v>1.0909090909090908</v>
       </c>
     </row>
@@ -49306,41 +49306,41 @@
       <c r="B8" s="65">
         <v>2</v>
       </c>
-      <c r="C8" s="225">
+      <c r="C8" s="207">
         <v>1</v>
       </c>
-      <c r="D8" s="225">
+      <c r="D8" s="207">
         <v>2</v>
       </c>
-      <c r="E8" s="225">
+      <c r="E8" s="207">
         <v>1</v>
       </c>
-      <c r="F8" s="225">
+      <c r="F8" s="207">
         <v>3</v>
       </c>
-      <c r="G8" s="225">
+      <c r="G8" s="207">
         <v>3</v>
       </c>
-      <c r="H8" s="225">
+      <c r="H8" s="207">
         <v>2</v>
       </c>
-      <c r="I8" s="225">
+      <c r="I8" s="207">
         <v>3</v>
       </c>
-      <c r="J8" s="225">
+      <c r="J8" s="207">
         <v>2</v>
       </c>
-      <c r="K8" s="225">
+      <c r="K8" s="207">
         <v>2</v>
       </c>
-      <c r="L8" s="225">
+      <c r="L8" s="207">
         <v>2</v>
       </c>
-      <c r="M8" s="225">
+      <c r="M8" s="207">
         <v>1</v>
       </c>
-      <c r="N8" s="222">
-        <f>AVERAGE(C8:M8)</f>
+      <c r="N8" s="204">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -49351,41 +49351,41 @@
       <c r="B9" s="65">
         <v>3</v>
       </c>
-      <c r="C9" s="225">
+      <c r="C9" s="207">
         <v>1</v>
       </c>
-      <c r="D9" s="225">
+      <c r="D9" s="207">
         <v>0</v>
       </c>
-      <c r="E9" s="225">
+      <c r="E9" s="207">
         <v>1</v>
       </c>
-      <c r="F9" s="225">
+      <c r="F9" s="207">
         <v>3</v>
       </c>
-      <c r="G9" s="225">
+      <c r="G9" s="207">
         <v>2</v>
       </c>
-      <c r="H9" s="225">
+      <c r="H9" s="207">
         <v>2</v>
       </c>
-      <c r="I9" s="225">
+      <c r="I9" s="207">
         <v>2</v>
       </c>
-      <c r="J9" s="225">
+      <c r="J9" s="207">
         <v>3</v>
       </c>
-      <c r="K9" s="225">
+      <c r="K9" s="207">
         <v>2</v>
       </c>
-      <c r="L9" s="225">
+      <c r="L9" s="207">
         <v>1</v>
       </c>
-      <c r="M9" s="225">
+      <c r="M9" s="207">
         <v>1</v>
       </c>
-      <c r="N9" s="222">
-        <f>AVERAGE(C9:M9)</f>
+      <c r="N9" s="204">
+        <f t="shared" si="0"/>
         <v>1.6363636363636365</v>
       </c>
     </row>
@@ -49393,44 +49393,44 @@
       <c r="A10" t="s">
         <v>499</v>
       </c>
-      <c r="B10" s="224">
+      <c r="B10" s="206">
         <v>4</v>
       </c>
-      <c r="C10" s="223">
+      <c r="C10" s="205">
         <v>0</v>
       </c>
-      <c r="D10" s="223">
+      <c r="D10" s="205">
         <v>0</v>
       </c>
-      <c r="E10" s="223">
+      <c r="E10" s="205">
         <v>1</v>
       </c>
-      <c r="F10" s="223">
+      <c r="F10" s="205">
         <v>1</v>
       </c>
-      <c r="G10" s="223">
+      <c r="G10" s="205">
         <v>2</v>
       </c>
-      <c r="H10" s="223">
+      <c r="H10" s="205">
         <v>1</v>
       </c>
-      <c r="I10" s="223">
+      <c r="I10" s="205">
         <v>1</v>
       </c>
-      <c r="J10" s="223">
+      <c r="J10" s="205">
         <v>1</v>
       </c>
-      <c r="K10" s="223">
+      <c r="K10" s="205">
         <v>1</v>
       </c>
-      <c r="L10" s="223">
+      <c r="L10" s="205">
         <v>0</v>
       </c>
-      <c r="M10" s="223">
+      <c r="M10" s="205">
         <v>1</v>
       </c>
-      <c r="N10" s="222">
-        <f>AVERAGE(C10:M10)</f>
+      <c r="N10" s="204">
+        <f t="shared" si="0"/>
         <v>0.81818181818181823</v>
       </c>
     </row>
@@ -49438,44 +49438,44 @@
       <c r="A11" t="s">
         <v>498</v>
       </c>
-      <c r="B11" s="224">
+      <c r="B11" s="206">
         <v>5</v>
       </c>
-      <c r="C11" s="223">
+      <c r="C11" s="205">
         <v>1</v>
       </c>
-      <c r="D11" s="223">
+      <c r="D11" s="205">
         <v>1</v>
       </c>
-      <c r="E11" s="223">
+      <c r="E11" s="205">
         <v>1</v>
       </c>
-      <c r="F11" s="223">
+      <c r="F11" s="205">
         <v>2</v>
       </c>
-      <c r="G11" s="223">
+      <c r="G11" s="205">
         <v>3</v>
       </c>
-      <c r="H11" s="223">
+      <c r="H11" s="205">
         <v>2</v>
       </c>
-      <c r="I11" s="223">
+      <c r="I11" s="205">
         <v>2</v>
       </c>
-      <c r="J11" s="223">
+      <c r="J11" s="205">
         <v>3</v>
       </c>
-      <c r="K11" s="223">
+      <c r="K11" s="205">
         <v>2</v>
       </c>
-      <c r="L11" s="223">
+      <c r="L11" s="205">
         <v>2</v>
       </c>
-      <c r="M11" s="223">
+      <c r="M11" s="205">
         <v>2</v>
       </c>
-      <c r="N11" s="222">
-        <f>AVERAGE(C11:M11)</f>
+      <c r="N11" s="204">
+        <f t="shared" si="0"/>
         <v>1.9090909090909092</v>
       </c>
     </row>
@@ -49483,44 +49483,44 @@
       <c r="A12" t="s">
         <v>497</v>
       </c>
-      <c r="B12" s="224">
+      <c r="B12" s="206">
         <v>6</v>
       </c>
-      <c r="C12" s="223">
+      <c r="C12" s="205">
         <v>0</v>
       </c>
-      <c r="D12" s="223">
+      <c r="D12" s="205">
         <v>0</v>
       </c>
-      <c r="E12" s="223">
+      <c r="E12" s="205">
         <v>1</v>
       </c>
-      <c r="F12" s="223">
+      <c r="F12" s="205">
         <v>2</v>
       </c>
-      <c r="G12" s="223">
+      <c r="G12" s="205">
         <v>1</v>
       </c>
-      <c r="H12" s="223">
+      <c r="H12" s="205">
         <v>1</v>
       </c>
-      <c r="I12" s="223">
+      <c r="I12" s="205">
         <v>2</v>
       </c>
-      <c r="J12" s="223">
+      <c r="J12" s="205">
         <v>1</v>
       </c>
-      <c r="K12" s="223">
+      <c r="K12" s="205">
         <v>2</v>
       </c>
-      <c r="L12" s="223">
+      <c r="L12" s="205">
         <v>1</v>
       </c>
-      <c r="M12" s="223">
+      <c r="M12" s="205">
         <v>0</v>
       </c>
-      <c r="N12" s="222">
-        <f>AVERAGE(C12:M12)</f>
+      <c r="N12" s="204">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -49528,44 +49528,44 @@
       <c r="A13" t="s">
         <v>495</v>
       </c>
-      <c r="B13" s="224">
+      <c r="B13" s="206">
         <v>7</v>
       </c>
-      <c r="C13" s="223">
+      <c r="C13" s="205">
         <v>0</v>
       </c>
-      <c r="D13" s="223">
+      <c r="D13" s="205">
         <v>1</v>
       </c>
-      <c r="E13" s="223">
+      <c r="E13" s="205">
         <v>1</v>
       </c>
-      <c r="F13" s="223">
+      <c r="F13" s="205">
         <v>1</v>
       </c>
-      <c r="G13" s="223">
+      <c r="G13" s="205">
         <v>2</v>
       </c>
-      <c r="H13" s="223">
+      <c r="H13" s="205">
         <v>2</v>
       </c>
-      <c r="I13" s="223">
+      <c r="I13" s="205">
         <v>1</v>
       </c>
-      <c r="J13" s="223">
+      <c r="J13" s="205">
         <v>0</v>
       </c>
-      <c r="K13" s="223">
+      <c r="K13" s="205">
         <v>0</v>
       </c>
-      <c r="L13" s="223">
+      <c r="L13" s="205">
         <v>1</v>
       </c>
-      <c r="M13" s="223">
+      <c r="M13" s="205">
         <v>0</v>
       </c>
-      <c r="N13" s="222">
-        <f>AVERAGE(C13:M13)</f>
+      <c r="N13" s="204">
+        <f t="shared" si="0"/>
         <v>0.81818181818181823</v>
       </c>
     </row>
@@ -49573,44 +49573,44 @@
       <c r="A14" t="s">
         <v>496</v>
       </c>
-      <c r="B14" s="224">
+      <c r="B14" s="206">
         <v>8</v>
       </c>
-      <c r="C14" s="223">
+      <c r="C14" s="205">
         <v>1</v>
       </c>
-      <c r="D14" s="223">
+      <c r="D14" s="205">
         <v>2</v>
       </c>
-      <c r="E14" s="223">
+      <c r="E14" s="205">
         <v>2</v>
       </c>
-      <c r="F14" s="223">
+      <c r="F14" s="205">
         <v>1</v>
       </c>
-      <c r="G14" s="223">
+      <c r="G14" s="205">
         <v>2</v>
       </c>
-      <c r="H14" s="223">
+      <c r="H14" s="205">
         <v>1</v>
       </c>
-      <c r="I14" s="223">
+      <c r="I14" s="205">
         <v>1</v>
       </c>
-      <c r="J14" s="223">
+      <c r="J14" s="205">
         <v>2</v>
       </c>
-      <c r="K14" s="223">
+      <c r="K14" s="205">
         <v>1</v>
       </c>
-      <c r="L14" s="223">
+      <c r="L14" s="205">
         <v>1</v>
       </c>
-      <c r="M14" s="223">
+      <c r="M14" s="205">
         <v>1</v>
       </c>
-      <c r="N14" s="222">
-        <f>AVERAGE(C14:M14)</f>
+      <c r="N14" s="204">
+        <f t="shared" si="0"/>
         <v>1.3636363636363635</v>
       </c>
     </row>
@@ -49618,44 +49618,44 @@
       <c r="A15" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="224">
+      <c r="B15" s="206">
         <v>9</v>
       </c>
-      <c r="C15" s="223">
+      <c r="C15" s="205">
         <v>0</v>
       </c>
-      <c r="D15" s="223">
+      <c r="D15" s="205">
         <v>1</v>
       </c>
-      <c r="E15" s="223">
+      <c r="E15" s="205">
         <v>2</v>
       </c>
-      <c r="F15" s="223">
+      <c r="F15" s="205">
         <v>1</v>
       </c>
-      <c r="G15" s="223">
+      <c r="G15" s="205">
         <v>2</v>
       </c>
-      <c r="H15" s="223">
+      <c r="H15" s="205">
         <v>2</v>
       </c>
-      <c r="I15" s="223">
+      <c r="I15" s="205">
         <v>2</v>
       </c>
-      <c r="J15" s="223">
+      <c r="J15" s="205">
         <v>1</v>
       </c>
-      <c r="K15" s="223">
+      <c r="K15" s="205">
         <v>2</v>
       </c>
-      <c r="L15" s="223">
+      <c r="L15" s="205">
         <v>2</v>
       </c>
-      <c r="M15" s="223">
+      <c r="M15" s="205">
         <v>2</v>
       </c>
-      <c r="N15" s="222">
-        <f>AVERAGE(C15:M15)</f>
+      <c r="N15" s="204">
+        <f t="shared" si="0"/>
         <v>1.5454545454545454</v>
       </c>
     </row>
@@ -49663,44 +49663,44 @@
       <c r="A16" t="s">
         <v>495</v>
       </c>
-      <c r="B16" s="224">
+      <c r="B16" s="206">
         <v>10</v>
       </c>
-      <c r="C16" s="223">
+      <c r="C16" s="205">
         <v>0</v>
       </c>
-      <c r="D16" s="223">
+      <c r="D16" s="205">
         <v>0</v>
       </c>
-      <c r="E16" s="223">
+      <c r="E16" s="205">
         <v>1</v>
       </c>
-      <c r="F16" s="223">
+      <c r="F16" s="205">
         <v>1</v>
       </c>
-      <c r="G16" s="223">
+      <c r="G16" s="205">
         <v>1</v>
       </c>
-      <c r="H16" s="223">
+      <c r="H16" s="205">
         <v>2</v>
       </c>
-      <c r="I16" s="223">
+      <c r="I16" s="205">
         <v>2</v>
       </c>
-      <c r="J16" s="223">
+      <c r="J16" s="205">
         <v>1</v>
       </c>
-      <c r="K16" s="223">
+      <c r="K16" s="205">
         <v>1</v>
       </c>
-      <c r="L16" s="223">
+      <c r="L16" s="205">
         <v>1</v>
       </c>
-      <c r="M16" s="223">
+      <c r="M16" s="205">
         <v>1</v>
       </c>
-      <c r="N16" s="222">
-        <f>AVERAGE(C16:M16)</f>
+      <c r="N16" s="204">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -49708,44 +49708,44 @@
       <c r="A17" t="s">
         <v>496</v>
       </c>
-      <c r="B17" s="224">
+      <c r="B17" s="206">
         <v>11</v>
       </c>
-      <c r="C17" s="223">
+      <c r="C17" s="205">
         <v>1</v>
       </c>
-      <c r="D17" s="223">
+      <c r="D17" s="205">
         <v>1</v>
       </c>
-      <c r="E17" s="223">
+      <c r="E17" s="205">
         <v>2</v>
       </c>
-      <c r="F17" s="223">
+      <c r="F17" s="205">
         <v>2</v>
       </c>
-      <c r="G17" s="223">
+      <c r="G17" s="205">
         <v>1</v>
       </c>
-      <c r="H17" s="223">
+      <c r="H17" s="205">
         <v>1</v>
       </c>
-      <c r="I17" s="223">
+      <c r="I17" s="205">
         <v>2</v>
       </c>
-      <c r="J17" s="223">
+      <c r="J17" s="205">
         <v>2</v>
       </c>
-      <c r="K17" s="223">
+      <c r="K17" s="205">
         <v>1</v>
       </c>
-      <c r="L17" s="223">
+      <c r="L17" s="205">
         <v>2</v>
       </c>
-      <c r="M17" s="223">
+      <c r="M17" s="205">
         <v>1</v>
       </c>
-      <c r="N17" s="222">
-        <f>AVERAGE(C17:M17)</f>
+      <c r="N17" s="204">
+        <f t="shared" si="0"/>
         <v>1.4545454545454546</v>
       </c>
     </row>
@@ -49753,44 +49753,44 @@
       <c r="A18" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="224">
+      <c r="B18" s="206">
         <v>12</v>
       </c>
-      <c r="C18" s="223">
+      <c r="C18" s="205">
         <v>0</v>
       </c>
-      <c r="D18" s="223">
+      <c r="D18" s="205">
         <v>1</v>
       </c>
-      <c r="E18" s="223">
+      <c r="E18" s="205">
         <v>0</v>
       </c>
-      <c r="F18" s="223">
+      <c r="F18" s="205">
         <v>1</v>
       </c>
-      <c r="G18" s="223">
+      <c r="G18" s="205">
         <v>1</v>
       </c>
-      <c r="H18" s="223">
+      <c r="H18" s="205">
         <v>2</v>
       </c>
-      <c r="I18" s="223">
+      <c r="I18" s="205">
         <v>0</v>
       </c>
-      <c r="J18" s="223">
+      <c r="J18" s="205">
         <v>2</v>
       </c>
-      <c r="K18" s="223">
+      <c r="K18" s="205">
         <v>1</v>
       </c>
-      <c r="L18" s="223">
+      <c r="L18" s="205">
         <v>1</v>
       </c>
-      <c r="M18" s="223">
+      <c r="M18" s="205">
         <v>1</v>
       </c>
-      <c r="N18" s="222">
-        <f>AVERAGE(C18:M18)</f>
+      <c r="N18" s="204">
+        <f t="shared" si="0"/>
         <v>0.90909090909090906</v>
       </c>
     </row>
@@ -58681,10 +58681,10 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="202" t="s">
+      <c r="B12" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="202"/>
+      <c r="C12" s="220"/>
       <c r="D12" s="35" t="s">
         <v>15</v>
       </c>
@@ -66604,10 +66604,10 @@
       <c r="N11" s="24"/>
     </row>
     <row r="12" spans="1:14" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="202" t="s">
+      <c r="B12" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="202"/>
+      <c r="C12" s="220"/>
       <c r="D12" s="12" t="s">
         <v>8</v>
       </c>

--- a/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_CropCanopy.xlsx
+++ b/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_CropCanopy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2023_F013B4_CO_TILL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728C4A64-2481-4704-818E-0E408A03FFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4711FB-CBF3-41C4-93EF-3EAF98C4F007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16455" yWindow="-28440" windowWidth="17805" windowHeight="11445" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1470" yWindow="-25290" windowWidth="17805" windowHeight="20370" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="12" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="505">
   <si>
     <t>01-</t>
   </si>
@@ -1607,6 +1607,9 @@
   <si>
     <t>date:</t>
   </si>
+  <si>
+    <t>PLPD</t>
+  </si>
 </sst>
 </file>
 
@@ -3113,7 +3116,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3122,28 +3143,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="21" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -17651,33 +17654,33 @@
       <c r="C11" s="186" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="227">
+      <c r="D11" s="232">
         <v>45048</v>
       </c>
-      <c r="E11" s="228"/>
-      <c r="F11" s="227">
+      <c r="E11" s="234"/>
+      <c r="F11" s="232">
         <v>45050</v>
       </c>
-      <c r="G11" s="228"/>
-      <c r="H11" s="227">
+      <c r="G11" s="234"/>
+      <c r="H11" s="232">
         <v>45054</v>
       </c>
-      <c r="I11" s="228"/>
-      <c r="J11" s="227">
+      <c r="I11" s="234"/>
+      <c r="J11" s="232">
         <v>45057</v>
       </c>
-      <c r="K11" s="236"/>
-      <c r="L11" s="228"/>
-      <c r="M11" s="227">
+      <c r="K11" s="233"/>
+      <c r="L11" s="234"/>
+      <c r="M11" s="232">
         <v>45061</v>
       </c>
-      <c r="N11" s="236"/>
-      <c r="O11" s="228"/>
-      <c r="P11" s="227">
+      <c r="N11" s="233"/>
+      <c r="O11" s="234"/>
+      <c r="P11" s="232">
         <v>45064</v>
       </c>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="228"/>
+      <c r="Q11" s="233"/>
+      <c r="R11" s="234"/>
     </row>
     <row r="12" spans="1:18" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="184" t="s">
@@ -17686,33 +17689,33 @@
       <c r="C12" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="229">
+      <c r="D12" s="235">
         <v>122</v>
       </c>
-      <c r="E12" s="230"/>
-      <c r="F12" s="229">
+      <c r="E12" s="229"/>
+      <c r="F12" s="235">
         <v>124</v>
       </c>
-      <c r="G12" s="230"/>
-      <c r="H12" s="229">
+      <c r="G12" s="229"/>
+      <c r="H12" s="235">
         <v>128</v>
       </c>
-      <c r="I12" s="230"/>
-      <c r="J12" s="229">
+      <c r="I12" s="229"/>
+      <c r="J12" s="235">
         <v>131</v>
       </c>
-      <c r="K12" s="237"/>
-      <c r="L12" s="230"/>
-      <c r="M12" s="229">
+      <c r="K12" s="236"/>
+      <c r="L12" s="229"/>
+      <c r="M12" s="235">
         <v>135</v>
       </c>
-      <c r="N12" s="237"/>
-      <c r="O12" s="230"/>
-      <c r="P12" s="229">
+      <c r="N12" s="236"/>
+      <c r="O12" s="229"/>
+      <c r="P12" s="235">
         <v>138</v>
       </c>
-      <c r="Q12" s="237"/>
-      <c r="R12" s="230"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="229"/>
     </row>
     <row r="13" spans="1:18" s="178" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="181" t="s">
@@ -17721,50 +17724,50 @@
       <c r="C13" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="233" t="s">
+      <c r="D13" s="227" t="s">
         <v>458</v>
       </c>
-      <c r="E13" s="230"/>
-      <c r="F13" s="233" t="s">
+      <c r="E13" s="229"/>
+      <c r="F13" s="227" t="s">
         <v>457</v>
       </c>
-      <c r="G13" s="230"/>
-      <c r="H13" s="233" t="s">
+      <c r="G13" s="229"/>
+      <c r="H13" s="227" t="s">
         <v>456</v>
       </c>
-      <c r="I13" s="230"/>
-      <c r="J13" s="233" t="s">
+      <c r="I13" s="229"/>
+      <c r="J13" s="227" t="s">
         <v>455</v>
       </c>
-      <c r="K13" s="235"/>
-      <c r="L13" s="230"/>
-      <c r="M13" s="233" t="s">
+      <c r="K13" s="228"/>
+      <c r="L13" s="229"/>
+      <c r="M13" s="227" t="s">
         <v>454</v>
       </c>
-      <c r="N13" s="235"/>
-      <c r="O13" s="230"/>
-      <c r="P13" s="233" t="s">
+      <c r="N13" s="228"/>
+      <c r="O13" s="229"/>
+      <c r="P13" s="227" t="s">
         <v>453</v>
       </c>
-      <c r="Q13" s="235"/>
-      <c r="R13" s="230"/>
+      <c r="Q13" s="228"/>
+      <c r="R13" s="229"/>
     </row>
     <row r="14" spans="1:18" s="131" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="174"/>
       <c r="B14" s="173"/>
       <c r="C14" s="172"/>
-      <c r="D14" s="231"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="234"/>
-      <c r="G14" s="232"/>
-      <c r="H14" s="234"/>
-      <c r="I14" s="232"/>
-      <c r="J14" s="234"/>
-      <c r="K14" s="234"/>
-      <c r="L14" s="232"/>
-      <c r="M14" s="234"/>
-      <c r="N14" s="234"/>
-      <c r="O14" s="232"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="231"/>
+      <c r="F14" s="230"/>
+      <c r="G14" s="231"/>
+      <c r="H14" s="230"/>
+      <c r="I14" s="231"/>
+      <c r="J14" s="230"/>
+      <c r="K14" s="230"/>
+      <c r="L14" s="231"/>
+      <c r="M14" s="230"/>
+      <c r="N14" s="230"/>
+      <c r="O14" s="231"/>
       <c r="P14" s="176"/>
       <c r="Q14" s="176"/>
       <c r="R14" s="175"/>
@@ -27011,6 +27014,18 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="J14:L14"/>
@@ -27022,18 +27037,6 @@
     <mergeCell ref="P13:R13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0.25"/>
@@ -27179,7 +27182,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="130">
-        <f t="shared" ref="I3:I34" si="0">H4/2</f>
+        <f t="shared" ref="I4:I34" si="0">H4/2</f>
         <v>4</v>
       </c>
       <c r="J4" s="134">
@@ -49818,7 +49821,7 @@
         <v>414</v>
       </c>
       <c r="B1" s="127" t="s">
-        <v>423</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">

--- a/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_CropCanopy.xlsx
+++ b/Data/2023_F013B4_CO_TILL/2023_F013B4_CO_TILL_CropCanopy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2023_F013B4_CO_TILL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4711FB-CBF3-41C4-93EF-3EAF98C4F007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4AA088-71F9-408E-8A80-9DB7579260E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1470" yWindow="-25290" windowWidth="17805" windowHeight="20370" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1335" yWindow="-21660" windowWidth="18030" windowHeight="16230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="12" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="504">
   <si>
     <t>01-</t>
   </si>
@@ -1343,9 +1343,6 @@
   </si>
   <si>
     <t>Final density counts</t>
-  </si>
-  <si>
-    <t>PLAPD</t>
   </si>
   <si>
     <t>03-15</t>
@@ -3116,25 +3113,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3143,10 +3122,28 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="21" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -14126,7 +14123,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F1" t="s">
-        <v>423</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -14965,7 +14962,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B46">
         <v>15</v>
@@ -17590,7 +17587,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="193" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -17603,7 +17600,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="190" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B4" s="189"/>
       <c r="C4" s="188"/>
@@ -17615,7 +17612,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="190" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B6" s="189"/>
       <c r="C6" s="188"/>
@@ -17625,7 +17622,7 @@
       <c r="B7" s="189"/>
       <c r="C7" s="188"/>
       <c r="F7" s="191" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -17634,17 +17631,17 @@
       <c r="C8" s="188"/>
       <c r="F8" s="188"/>
       <c r="G8" s="130" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9" s="130" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="130" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17654,33 +17651,33 @@
       <c r="C11" s="186" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="232">
+      <c r="D11" s="227">
         <v>45048</v>
       </c>
-      <c r="E11" s="234"/>
-      <c r="F11" s="232">
+      <c r="E11" s="228"/>
+      <c r="F11" s="227">
         <v>45050</v>
       </c>
-      <c r="G11" s="234"/>
-      <c r="H11" s="232">
+      <c r="G11" s="228"/>
+      <c r="H11" s="227">
         <v>45054</v>
       </c>
-      <c r="I11" s="234"/>
-      <c r="J11" s="232">
+      <c r="I11" s="228"/>
+      <c r="J11" s="227">
         <v>45057</v>
       </c>
-      <c r="K11" s="233"/>
-      <c r="L11" s="234"/>
-      <c r="M11" s="232">
+      <c r="K11" s="236"/>
+      <c r="L11" s="228"/>
+      <c r="M11" s="227">
         <v>45061</v>
       </c>
-      <c r="N11" s="233"/>
-      <c r="O11" s="234"/>
-      <c r="P11" s="232">
+      <c r="N11" s="236"/>
+      <c r="O11" s="228"/>
+      <c r="P11" s="227">
         <v>45064</v>
       </c>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="234"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="228"/>
     </row>
     <row r="12" spans="1:18" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="184" t="s">
@@ -17689,33 +17686,33 @@
       <c r="C12" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="235">
+      <c r="D12" s="229">
         <v>122</v>
       </c>
-      <c r="E12" s="229"/>
-      <c r="F12" s="235">
+      <c r="E12" s="230"/>
+      <c r="F12" s="229">
         <v>124</v>
       </c>
-      <c r="G12" s="229"/>
-      <c r="H12" s="235">
+      <c r="G12" s="230"/>
+      <c r="H12" s="229">
         <v>128</v>
       </c>
-      <c r="I12" s="229"/>
-      <c r="J12" s="235">
+      <c r="I12" s="230"/>
+      <c r="J12" s="229">
         <v>131</v>
       </c>
-      <c r="K12" s="236"/>
-      <c r="L12" s="229"/>
-      <c r="M12" s="235">
+      <c r="K12" s="237"/>
+      <c r="L12" s="230"/>
+      <c r="M12" s="229">
         <v>135</v>
       </c>
-      <c r="N12" s="236"/>
-      <c r="O12" s="229"/>
-      <c r="P12" s="235">
+      <c r="N12" s="237"/>
+      <c r="O12" s="230"/>
+      <c r="P12" s="229">
         <v>138</v>
       </c>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="229"/>
+      <c r="Q12" s="237"/>
+      <c r="R12" s="230"/>
     </row>
     <row r="13" spans="1:18" s="178" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="181" t="s">
@@ -17724,50 +17721,50 @@
       <c r="C13" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="227" t="s">
-        <v>458</v>
-      </c>
-      <c r="E13" s="229"/>
-      <c r="F13" s="227" t="s">
+      <c r="D13" s="233" t="s">
         <v>457</v>
       </c>
-      <c r="G13" s="229"/>
-      <c r="H13" s="227" t="s">
+      <c r="E13" s="230"/>
+      <c r="F13" s="233" t="s">
         <v>456</v>
       </c>
-      <c r="I13" s="229"/>
-      <c r="J13" s="227" t="s">
+      <c r="G13" s="230"/>
+      <c r="H13" s="233" t="s">
         <v>455</v>
       </c>
-      <c r="K13" s="228"/>
-      <c r="L13" s="229"/>
-      <c r="M13" s="227" t="s">
+      <c r="I13" s="230"/>
+      <c r="J13" s="233" t="s">
         <v>454</v>
       </c>
-      <c r="N13" s="228"/>
-      <c r="O13" s="229"/>
-      <c r="P13" s="227" t="s">
+      <c r="K13" s="235"/>
+      <c r="L13" s="230"/>
+      <c r="M13" s="233" t="s">
         <v>453</v>
       </c>
-      <c r="Q13" s="228"/>
-      <c r="R13" s="229"/>
+      <c r="N13" s="235"/>
+      <c r="O13" s="230"/>
+      <c r="P13" s="233" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q13" s="235"/>
+      <c r="R13" s="230"/>
     </row>
     <row r="14" spans="1:18" s="131" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="174"/>
       <c r="B14" s="173"/>
       <c r="C14" s="172"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="231"/>
-      <c r="F14" s="230"/>
-      <c r="G14" s="231"/>
-      <c r="H14" s="230"/>
-      <c r="I14" s="231"/>
-      <c r="J14" s="230"/>
-      <c r="K14" s="230"/>
-      <c r="L14" s="231"/>
-      <c r="M14" s="230"/>
-      <c r="N14" s="230"/>
-      <c r="O14" s="231"/>
+      <c r="D14" s="231"/>
+      <c r="E14" s="232"/>
+      <c r="F14" s="234"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="234"/>
+      <c r="I14" s="232"/>
+      <c r="J14" s="234"/>
+      <c r="K14" s="234"/>
+      <c r="L14" s="232"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="234"/>
+      <c r="O14" s="232"/>
       <c r="P14" s="176"/>
       <c r="Q14" s="176"/>
       <c r="R14" s="175"/>
@@ -17779,47 +17776,47 @@
       </c>
       <c r="C15" s="172"/>
       <c r="D15" s="171" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E15" s="169"/>
       <c r="F15" s="170" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G15" s="169" t="s">
+        <v>450</v>
+      </c>
+      <c r="H15" s="170" t="s">
         <v>451</v>
       </c>
-      <c r="H15" s="170" t="s">
-        <v>452</v>
-      </c>
       <c r="I15" s="169" t="s">
+        <v>450</v>
+      </c>
+      <c r="J15" s="170" t="s">
         <v>451</v>
       </c>
-      <c r="J15" s="170" t="s">
-        <v>452</v>
-      </c>
       <c r="K15" s="169" t="s">
+        <v>450</v>
+      </c>
+      <c r="L15" s="169" t="s">
+        <v>449</v>
+      </c>
+      <c r="M15" s="171" t="s">
         <v>451</v>
       </c>
-      <c r="L15" s="169" t="s">
+      <c r="N15" s="170" t="s">
         <v>450</v>
       </c>
-      <c r="M15" s="171" t="s">
-        <v>452</v>
-      </c>
-      <c r="N15" s="170" t="s">
+      <c r="O15" s="169" t="s">
+        <v>449</v>
+      </c>
+      <c r="P15" s="170" t="s">
         <v>451</v>
       </c>
-      <c r="O15" s="169" t="s">
+      <c r="Q15" s="169" t="s">
         <v>450</v>
       </c>
-      <c r="P15" s="170" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q15" s="169" t="s">
-        <v>451</v>
-      </c>
       <c r="R15" s="169" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -17828,7 +17825,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D16" s="157">
         <v>0</v>
@@ -17870,7 +17867,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D17" s="147">
         <v>1</v>
@@ -17914,7 +17911,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D18" s="147">
         <v>1</v>
@@ -17956,7 +17953,7 @@
         <v>33</v>
       </c>
       <c r="C19" s="150" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D19" s="147">
         <v>1</v>
@@ -17996,7 +17993,7 @@
         <v>35</v>
       </c>
       <c r="C20" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D20" s="147">
         <v>1</v>
@@ -18038,7 +18035,7 @@
         <v>37</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D21" s="147">
         <v>0</v>
@@ -18080,7 +18077,7 @@
         <v>39</v>
       </c>
       <c r="C22" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D22" s="147">
         <v>0</v>
@@ -18124,7 +18121,7 @@
         <v>41</v>
       </c>
       <c r="C23" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D23" s="147">
         <v>0</v>
@@ -18166,7 +18163,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D24" s="147">
         <v>0</v>
@@ -18206,7 +18203,7 @@
         <v>45</v>
       </c>
       <c r="C25" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D25" s="147">
         <v>0</v>
@@ -18254,7 +18251,7 @@
         <v>47</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D26" s="147">
         <v>0</v>
@@ -18300,7 +18297,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D27" s="147">
         <v>0</v>
@@ -18346,7 +18343,7 @@
         <v>51</v>
       </c>
       <c r="C28" s="150" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D28" s="147">
         <v>0</v>
@@ -18392,7 +18389,7 @@
         <v>53</v>
       </c>
       <c r="C29" s="150" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D29" s="147">
         <v>0</v>
@@ -18438,7 +18435,7 @@
         <v>55</v>
       </c>
       <c r="C30" s="143" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D30" s="140">
         <v>1</v>
@@ -18484,7 +18481,7 @@
         <v>56</v>
       </c>
       <c r="C31" s="154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D31" s="157">
         <v>3</v>
@@ -18532,7 +18529,7 @@
         <v>58</v>
       </c>
       <c r="C32" s="154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D32" s="147">
         <v>0</v>
@@ -18580,7 +18577,7 @@
         <v>60</v>
       </c>
       <c r="C33" s="154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D33" s="147">
         <v>1</v>
@@ -18626,7 +18623,7 @@
         <v>62</v>
       </c>
       <c r="C34" s="150" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D34" s="147">
         <v>3</v>
@@ -18674,7 +18671,7 @@
         <v>64</v>
       </c>
       <c r="C35" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D35" s="147">
         <v>3</v>
@@ -18716,7 +18713,7 @@
         <v>66</v>
       </c>
       <c r="C36" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D36" s="147">
         <v>2</v>
@@ -18760,7 +18757,7 @@
         <v>68</v>
       </c>
       <c r="C37" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D37" s="147">
         <v>1</v>
@@ -18804,7 +18801,7 @@
         <v>70</v>
       </c>
       <c r="C38" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D38" s="147">
         <v>0</v>
@@ -18846,7 +18843,7 @@
         <v>72</v>
       </c>
       <c r="C39" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D39" s="147">
         <v>4</v>
@@ -18892,7 +18889,7 @@
         <v>74</v>
       </c>
       <c r="C40" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D40" s="147">
         <v>0</v>
@@ -18936,7 +18933,7 @@
         <v>76</v>
       </c>
       <c r="C41" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D41" s="147">
         <v>3</v>
@@ -18980,7 +18977,7 @@
         <v>78</v>
       </c>
       <c r="C42" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D42" s="147">
         <v>5</v>
@@ -19024,7 +19021,7 @@
         <v>80</v>
       </c>
       <c r="C43" s="150" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D43" s="147">
         <v>4</v>
@@ -19070,7 +19067,7 @@
         <v>82</v>
       </c>
       <c r="C44" s="150" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D44" s="147">
         <v>4</v>
@@ -19112,7 +19109,7 @@
         <v>84</v>
       </c>
       <c r="C45" s="143" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D45" s="140">
         <v>2</v>
@@ -19154,7 +19151,7 @@
         <v>28</v>
       </c>
       <c r="C46" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D46" s="157">
         <v>8</v>
@@ -19200,7 +19197,7 @@
         <v>30</v>
       </c>
       <c r="C47" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D47" s="147">
         <v>2</v>
@@ -19246,7 +19243,7 @@
         <v>32</v>
       </c>
       <c r="C48" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D48" s="147">
         <v>1</v>
@@ -19288,7 +19285,7 @@
         <v>34</v>
       </c>
       <c r="C49" s="150" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D49" s="147">
         <v>6</v>
@@ -19334,7 +19331,7 @@
         <v>36</v>
       </c>
       <c r="C50" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D50" s="147">
         <v>4</v>
@@ -19380,7 +19377,7 @@
         <v>38</v>
       </c>
       <c r="C51" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D51" s="147">
         <v>6</v>
@@ -19424,7 +19421,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D52" s="147">
         <v>0</v>
@@ -19464,7 +19461,7 @@
         <v>42</v>
       </c>
       <c r="C53" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D53" s="147">
         <v>6</v>
@@ -19507,7 +19504,7 @@
         <v>44</v>
       </c>
       <c r="C54" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D54" s="147">
         <v>3</v>
@@ -19549,7 +19546,7 @@
         <v>46</v>
       </c>
       <c r="C55" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D55" s="147">
         <v>5</v>
@@ -19593,7 +19590,7 @@
         <v>48</v>
       </c>
       <c r="C56" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D56" s="147">
         <v>1</v>
@@ -19635,7 +19632,7 @@
         <v>50</v>
       </c>
       <c r="C57" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D57" s="147">
         <v>4</v>
@@ -19683,7 +19680,7 @@
         <v>52</v>
       </c>
       <c r="C58" s="150" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D58" s="147">
         <v>1</v>
@@ -19729,7 +19726,7 @@
         <v>54</v>
       </c>
       <c r="C59" s="150" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D59" s="147">
         <v>5</v>
@@ -19771,7 +19768,7 @@
         <v>55</v>
       </c>
       <c r="C60" s="143" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D60" s="140">
         <v>7</v>
@@ -19815,7 +19812,7 @@
         <v>57</v>
       </c>
       <c r="C61" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D61" s="157">
         <v>0</v>
@@ -19861,7 +19858,7 @@
         <v>59</v>
       </c>
       <c r="C62" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D62" s="147">
         <v>0</v>
@@ -19907,7 +19904,7 @@
         <v>61</v>
       </c>
       <c r="C63" s="154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D63" s="147">
         <v>0</v>
@@ -25533,7 +25530,7 @@
         <v>138</v>
       </c>
       <c r="K206" s="130" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="2:18" x14ac:dyDescent="0.25">
@@ -25567,7 +25564,7 @@
         <v>127.44632768361582</v>
       </c>
       <c r="M207" s="130" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="208" spans="2:18" x14ac:dyDescent="0.25">
@@ -25663,7 +25660,7 @@
         <v>127.75206611570248</v>
       </c>
       <c r="M210" s="130" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="211" spans="2:18" x14ac:dyDescent="0.25">
@@ -25788,7 +25785,7 @@
     </row>
     <row r="222" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B222" s="137" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="223" spans="2:18" x14ac:dyDescent="0.25">
@@ -25816,7 +25813,7 @@
     </row>
     <row r="224" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B224" s="132" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D224" s="135">
         <f>AVERAGE(D16:D30)</f>
@@ -25858,7 +25855,7 @@
     </row>
     <row r="225" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B225" s="132" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D225" s="135">
         <f>AVERAGE(D31:D45)</f>
@@ -25900,7 +25897,7 @@
     </row>
     <row r="226" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B226" s="132" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D226" s="135">
         <f>AVERAGE(D46:D60)</f>
@@ -25942,7 +25939,7 @@
     </row>
     <row r="227" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B227" s="132" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D227" s="135">
         <f>AVERAGE(D61:D75)</f>
@@ -25983,7 +25980,7 @@
     </row>
     <row r="228" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B228" s="132" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D228" s="135">
         <f>AVERAGE(D76:D90)</f>
@@ -26025,7 +26022,7 @@
     </row>
     <row r="229" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B229" s="132" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D229" s="135">
         <f>AVERAGE(D91:D105)</f>
@@ -26067,7 +26064,7 @@
     </row>
     <row r="230" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B230" s="132" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D230" s="135">
         <f>AVERAGE(D106:D120)</f>
@@ -26108,7 +26105,7 @@
     </row>
     <row r="231" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B231" s="132" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D231" s="135">
         <f>AVERAGE(D121:D135)</f>
@@ -26149,7 +26146,7 @@
     </row>
     <row r="232" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B232" s="132" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D232" s="135">
         <f>AVERAGE(D136:D150)</f>
@@ -26191,7 +26188,7 @@
     </row>
     <row r="233" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B233" s="132" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D233" s="135">
         <f>AVERAGE(D151:D165)</f>
@@ -26232,7 +26229,7 @@
     </row>
     <row r="234" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B234" s="132" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D234" s="135">
         <f>AVERAGE(D166:D180)</f>
@@ -26273,7 +26270,7 @@
     </row>
     <row r="235" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B235" s="132" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D235" s="135">
         <f>AVERAGE(D181:D195)</f>
@@ -26314,10 +26311,10 @@
     </row>
     <row r="237" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B237" s="137" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L237" s="130" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="238" spans="2:18" x14ac:dyDescent="0.25">
@@ -26346,12 +26343,12 @@
         <v>0.5</v>
       </c>
       <c r="L238" s="130" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="239" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B239" s="132" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D239" s="135">
         <v>0.33333333333333331</v>
@@ -26383,7 +26380,7 @@
     </row>
     <row r="240" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B240" s="132" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D240" s="135">
         <v>2.3333333333333335</v>
@@ -26415,7 +26412,7 @@
     </row>
     <row r="241" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B241" s="132" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D241" s="135">
         <v>3.9333333333333331</v>
@@ -26446,7 +26443,7 @@
     </row>
     <row r="242" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B242" s="132" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D242" s="135">
         <v>0.33333333333333331</v>
@@ -26478,7 +26475,7 @@
     </row>
     <row r="243" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B243" s="132" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D243" s="135">
         <v>2.6</v>
@@ -26510,7 +26507,7 @@
     </row>
     <row r="244" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B244" s="132" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D244" s="135">
         <v>0.93333333333333335</v>
@@ -26542,7 +26539,7 @@
     </row>
     <row r="245" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B245" s="132" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D245" s="135">
         <v>0.93333333333333335</v>
@@ -26574,7 +26571,7 @@
     </row>
     <row r="246" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B246" s="132" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D246" s="135">
         <v>2.4</v>
@@ -26606,7 +26603,7 @@
     </row>
     <row r="247" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B247" s="132" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D247" s="135">
         <v>1.2666666666666666</v>
@@ -26638,7 +26635,7 @@
     </row>
     <row r="248" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B248" s="132" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D248" s="135">
         <v>0</v>
@@ -26670,7 +26667,7 @@
     </row>
     <row r="249" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B249" s="132" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D249" s="135">
         <v>2.6</v>
@@ -26702,7 +26699,7 @@
     </row>
     <row r="250" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B250" s="132" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D250" s="135">
         <v>0.4</v>
@@ -26734,10 +26731,10 @@
     </row>
     <row r="252" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B252" s="137" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L252" s="130" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="253" spans="2:14" x14ac:dyDescent="0.25">
@@ -26757,12 +26754,12 @@
         <v>0.5</v>
       </c>
       <c r="L253" s="130" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="254" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B254" s="132" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D254" s="135">
         <v>1</v>
@@ -26783,7 +26780,7 @@
     </row>
     <row r="255" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B255" s="132" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D255" s="135">
         <v>1.1428571428571428</v>
@@ -26804,7 +26801,7 @@
     </row>
     <row r="256" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B256" s="132" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D256" s="135">
         <v>1.4285714285714286</v>
@@ -26825,7 +26822,7 @@
     </row>
     <row r="257" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B257" s="132" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D257" s="135">
         <v>0</v>
@@ -26846,7 +26843,7 @@
     </row>
     <row r="258" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B258" s="132" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D258" s="135">
         <v>1.3333333333333333</v>
@@ -26867,7 +26864,7 @@
     </row>
     <row r="259" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B259" s="132" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D259" s="135">
         <v>1</v>
@@ -26888,7 +26885,7 @@
     </row>
     <row r="260" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B260" s="132" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D260" s="135">
         <v>0</v>
@@ -26909,7 +26906,7 @@
     </row>
     <row r="261" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B261" s="132" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D261" s="135">
         <v>0</v>
@@ -26930,7 +26927,7 @@
     </row>
     <row r="262" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B262" s="132" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D262" s="135">
         <v>1</v>
@@ -26951,7 +26948,7 @@
     </row>
     <row r="263" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B263" s="132" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D263" s="135">
         <v>0</v>
@@ -26972,7 +26969,7 @@
     </row>
     <row r="264" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B264" s="132" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D264" s="135">
         <v>0</v>
@@ -26993,7 +26990,7 @@
     </row>
     <row r="265" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B265" s="132" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D265" s="135">
         <v>0</v>
@@ -27014,18 +27011,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="J14:L14"/>
@@ -27037,6 +27022,18 @@
     <mergeCell ref="P13:R13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0.25"/>
@@ -27063,10 +27060,10 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C1" s="130" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L1" s="130" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -27092,7 +27089,7 @@
         <v>0.5</v>
       </c>
       <c r="J2" s="130" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L2" s="130">
         <v>131</v>
@@ -27104,7 +27101,7 @@
         <v>138</v>
       </c>
       <c r="O2" s="130" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q2" s="134"/>
     </row>
@@ -27113,7 +27110,7 @@
         <v>27</v>
       </c>
       <c r="B3" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C3" s="130">
         <v>0</v>
@@ -27161,7 +27158,7 @@
         <v>29</v>
       </c>
       <c r="B4" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C4" s="130">
         <v>1</v>
@@ -27209,7 +27206,7 @@
         <v>31</v>
       </c>
       <c r="B5" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C5" s="130">
         <v>1</v>
@@ -27257,7 +27254,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C6" s="130">
         <v>1</v>
@@ -27305,7 +27302,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C7" s="130">
         <v>1</v>
@@ -27353,7 +27350,7 @@
         <v>37</v>
       </c>
       <c r="B8" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C8" s="130">
         <v>0</v>
@@ -27401,7 +27398,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C9" s="130">
         <v>0</v>
@@ -27449,7 +27446,7 @@
         <v>41</v>
       </c>
       <c r="B10" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C10" s="130">
         <v>0</v>
@@ -27497,7 +27494,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C11" s="130">
         <v>0</v>
@@ -27545,7 +27542,7 @@
         <v>45</v>
       </c>
       <c r="B12" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C12" s="130">
         <v>0</v>
@@ -27593,7 +27590,7 @@
         <v>47</v>
       </c>
       <c r="B13" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C13" s="130">
         <v>0</v>
@@ -27641,7 +27638,7 @@
         <v>49</v>
       </c>
       <c r="B14" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C14" s="130">
         <v>0</v>
@@ -27688,7 +27685,7 @@
         <v>51</v>
       </c>
       <c r="B15" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C15" s="130">
         <v>0</v>
@@ -27735,7 +27732,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C16" s="130">
         <v>0</v>
@@ -27782,7 +27779,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C17" s="130">
         <v>1</v>
@@ -27830,7 +27827,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C18" s="130">
         <v>2</v>
@@ -27877,7 +27874,7 @@
         <v>82</v>
       </c>
       <c r="B19" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C19" s="130">
         <v>4</v>
@@ -27924,7 +27921,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C20" s="130">
         <v>4</v>
@@ -27971,7 +27968,7 @@
         <v>78</v>
       </c>
       <c r="B21" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C21" s="130">
         <v>5</v>
@@ -28018,7 +28015,7 @@
         <v>76</v>
       </c>
       <c r="B22" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C22" s="130">
         <v>3</v>
@@ -28065,7 +28062,7 @@
         <v>74</v>
       </c>
       <c r="B23" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C23" s="130">
         <v>0</v>
@@ -28112,7 +28109,7 @@
         <v>72</v>
       </c>
       <c r="B24" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C24" s="130">
         <v>4</v>
@@ -28159,7 +28156,7 @@
         <v>70</v>
       </c>
       <c r="B25" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C25" s="130">
         <v>0</v>
@@ -28206,7 +28203,7 @@
         <v>68</v>
       </c>
       <c r="B26" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C26" s="130">
         <v>1</v>
@@ -28253,7 +28250,7 @@
         <v>66</v>
       </c>
       <c r="B27" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C27" s="130">
         <v>2</v>
@@ -28300,7 +28297,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C28" s="130">
         <v>3</v>
@@ -28347,7 +28344,7 @@
         <v>62</v>
       </c>
       <c r="B29" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C29" s="130">
         <v>3</v>
@@ -28394,7 +28391,7 @@
         <v>60</v>
       </c>
       <c r="B30" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C30" s="130">
         <v>1</v>
@@ -28441,7 +28438,7 @@
         <v>58</v>
       </c>
       <c r="B31" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C31" s="130">
         <v>0</v>
@@ -28488,7 +28485,7 @@
         <v>56</v>
       </c>
       <c r="B32" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C32" s="130">
         <v>3</v>
@@ -28536,7 +28533,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C33" s="130">
         <v>8</v>
@@ -28583,7 +28580,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C34" s="130">
         <v>2</v>
@@ -28630,7 +28627,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C35" s="130">
         <v>1</v>
@@ -28675,7 +28672,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C36" s="130">
         <v>6</v>
@@ -28722,7 +28719,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C37" s="130">
         <v>4</v>
@@ -28769,7 +28766,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C38" s="130">
         <v>6</v>
@@ -28816,7 +28813,7 @@
         <v>40</v>
       </c>
       <c r="B39" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C39" s="130">
         <v>0</v>
@@ -28860,7 +28857,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C40" s="130">
         <v>6</v>
@@ -28907,7 +28904,7 @@
         <v>44</v>
       </c>
       <c r="B41" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C41" s="130">
         <v>3</v>
@@ -28954,7 +28951,7 @@
         <v>46</v>
       </c>
       <c r="B42" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C42" s="130">
         <v>5</v>
@@ -29001,7 +28998,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C43" s="130">
         <v>1</v>
@@ -29048,7 +29045,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C44" s="130">
         <v>4</v>
@@ -29095,7 +29092,7 @@
         <v>52</v>
       </c>
       <c r="B45" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C45" s="130">
         <v>1</v>
@@ -29142,7 +29139,7 @@
         <v>54</v>
       </c>
       <c r="B46" s="130" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C46" s="130">
         <v>5</v>
@@ -29186,10 +29183,10 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="130" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B47" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C47" s="130">
         <v>7</v>
@@ -29764,7 +29761,7 @@
         <v>61</v>
       </c>
       <c r="B60" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C60" s="130">
         <v>0</v>
@@ -29811,7 +29808,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C61" s="130">
         <v>0</v>
@@ -29858,7 +29855,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C62" s="130">
         <v>0</v>
@@ -35207,7 +35204,7 @@
       </c>
       <c r="B1" s="195"/>
       <c r="D1" s="200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E1" s="200"/>
       <c r="F1" s="200" t="s">
@@ -35222,7 +35219,7 @@
     <row r="3" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="196"/>
       <c r="B3" s="193" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C3" s="193"/>
     </row>
@@ -35232,7 +35229,7 @@
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="190"/>
       <c r="B5" s="192" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -35306,25 +35303,25 @@
         <v>7</v>
       </c>
       <c r="C11" s="199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D11" s="199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E11" s="199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F11" s="199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G11" s="199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H11" s="199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J11" s="131" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -39167,7 +39164,7 @@
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B195" s="202" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C195" s="203">
         <f>AVERAGE(C12:C26)</f>
@@ -39188,7 +39185,7 @@
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B196" s="202" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C196" s="203">
         <f>AVERAGE(C27:C41)</f>
@@ -39209,7 +39206,7 @@
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B197" s="202" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C197" s="203">
         <f>AVERAGE(C42:C56)</f>
@@ -39230,7 +39227,7 @@
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B198" s="202" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C198" s="203">
         <f>AVERAGE(C57:C71)</f>
@@ -39251,7 +39248,7 @@
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B199" s="202" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C199" s="203">
         <f>AVERAGE(C72:C86)</f>
@@ -39272,7 +39269,7 @@
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200" s="202" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C200" s="203">
         <f>AVERAGE(C87:C101)</f>
@@ -39293,7 +39290,7 @@
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B201" s="202" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C201" s="203">
         <f>AVERAGE(C102:C116)</f>
@@ -39314,7 +39311,7 @@
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B202" s="202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C202" s="203">
         <f>AVERAGE(C117:C131)</f>
@@ -39335,7 +39332,7 @@
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B203" s="202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C203" s="203">
         <f>AVERAGE(C132:C146)</f>
@@ -39356,7 +39353,7 @@
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B204" s="202" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C204" s="203">
         <f>AVERAGE(C147:C161)</f>
@@ -39377,7 +39374,7 @@
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B205" s="202" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C205" s="203">
         <f>AVERAGE(C162:C176)</f>
@@ -39398,7 +39395,7 @@
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B206" s="202" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C206" s="203">
         <f>AVERAGE(C177:C191)</f>
@@ -39453,7 +39450,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F1" s="215">
         <v>45110</v>
@@ -39472,7 +39469,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -39483,7 +39480,7 @@
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C4" s="239"/>
       <c r="D4" s="239"/>
@@ -39551,12 +39548,12 @@
         <v>21</v>
       </c>
       <c r="N6" s="209" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B7" s="11">
         <v>1</v>
@@ -39601,7 +39598,7 @@
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B8" s="65">
         <v>2</v>
@@ -39646,7 +39643,7 @@
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9" s="65">
         <v>3</v>
@@ -39691,7 +39688,7 @@
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10" s="206">
         <v>4</v>
@@ -39736,7 +39733,7 @@
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B11" s="206">
         <v>5</v>
@@ -39781,7 +39778,7 @@
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12" s="206">
         <v>6</v>
@@ -39826,7 +39823,7 @@
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B13" s="206">
         <v>7</v>
@@ -39871,7 +39868,7 @@
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B14" s="206">
         <v>8</v>
@@ -39916,7 +39913,7 @@
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B15" s="206">
         <v>9</v>
@@ -39961,7 +39958,7 @@
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="206">
         <v>10</v>
@@ -40006,7 +40003,7 @@
     </row>
     <row r="17" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="206">
         <v>11</v>
@@ -40051,7 +40048,7 @@
     </row>
     <row r="18" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B18" s="206">
         <v>12</v>
@@ -40124,7 +40121,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F1" s="215">
         <v>45120</v>
@@ -40143,7 +40140,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -40154,7 +40151,7 @@
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C4" s="239"/>
       <c r="D4" s="239"/>
@@ -40222,12 +40219,12 @@
         <v>21</v>
       </c>
       <c r="N6" s="209" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B7" s="11">
         <v>1</v>
@@ -40272,7 +40269,7 @@
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B8" s="65">
         <v>2</v>
@@ -40317,7 +40314,7 @@
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9" s="65">
         <v>3</v>
@@ -40362,7 +40359,7 @@
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10" s="206">
         <v>4</v>
@@ -40407,7 +40404,7 @@
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B11" s="206">
         <v>5</v>
@@ -40452,7 +40449,7 @@
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12" s="206">
         <v>6</v>
@@ -40497,7 +40494,7 @@
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B13" s="206">
         <v>7</v>
@@ -40542,7 +40539,7 @@
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B14" s="206">
         <v>8</v>
@@ -40587,7 +40584,7 @@
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B15" s="206">
         <v>9</v>
@@ -40632,7 +40629,7 @@
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="206">
         <v>10</v>
@@ -40677,7 +40674,7 @@
     </row>
     <row r="17" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="206">
         <v>11</v>
@@ -40722,7 +40719,7 @@
     </row>
     <row r="18" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B18" s="206">
         <v>12</v>
@@ -40795,7 +40792,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F1" s="215">
         <v>45127</v>
@@ -40814,7 +40811,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -40825,7 +40822,7 @@
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C4" s="239"/>
       <c r="D4" s="239"/>
@@ -40893,12 +40890,12 @@
         <v>21</v>
       </c>
       <c r="N6" s="209" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B7" s="11">
         <v>1</v>
@@ -40943,7 +40940,7 @@
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B8" s="65">
         <v>2</v>
@@ -40988,7 +40985,7 @@
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9" s="65">
         <v>3</v>
@@ -41033,7 +41030,7 @@
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10" s="206">
         <v>4</v>
@@ -41078,7 +41075,7 @@
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B11" s="206">
         <v>5</v>
@@ -41123,7 +41120,7 @@
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12" s="206">
         <v>6</v>
@@ -41168,7 +41165,7 @@
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B13" s="206">
         <v>7</v>
@@ -41213,7 +41210,7 @@
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B14" s="206">
         <v>8</v>
@@ -41258,7 +41255,7 @@
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B15" s="206">
         <v>9</v>
@@ -41303,7 +41300,7 @@
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="206">
         <v>10</v>
@@ -41348,7 +41345,7 @@
     </row>
     <row r="17" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="206">
         <v>11</v>
@@ -41393,7 +41390,7 @@
     </row>
     <row r="18" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B18" s="206">
         <v>12</v>
@@ -41466,7 +41463,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F1" s="215">
         <v>45134</v>
@@ -41485,7 +41482,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -41496,7 +41493,7 @@
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C4" s="239"/>
       <c r="D4" s="239"/>
@@ -41564,12 +41561,12 @@
         <v>21</v>
       </c>
       <c r="N6" s="209" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B7" s="11">
         <v>1</v>
@@ -41614,7 +41611,7 @@
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B8" s="65">
         <v>2</v>
@@ -41659,7 +41656,7 @@
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9" s="65">
         <v>3</v>
@@ -41704,7 +41701,7 @@
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10" s="206">
         <v>4</v>
@@ -41749,7 +41746,7 @@
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B11" s="206">
         <v>5</v>
@@ -41794,7 +41791,7 @@
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12" s="206">
         <v>6</v>
@@ -41839,7 +41836,7 @@
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B13" s="206">
         <v>7</v>
@@ -41884,7 +41881,7 @@
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B14" s="206">
         <v>8</v>
@@ -41929,7 +41926,7 @@
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B15" s="206">
         <v>9</v>
@@ -41974,7 +41971,7 @@
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="206">
         <v>10</v>
@@ -42019,7 +42016,7 @@
     </row>
     <row r="17" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="206">
         <v>11</v>
@@ -42064,7 +42061,7 @@
     </row>
     <row r="18" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B18" s="206">
         <v>12</v>
@@ -42137,7 +42134,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F1" s="215">
         <v>45141</v>
@@ -42156,7 +42153,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -42167,7 +42164,7 @@
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C4" s="239"/>
       <c r="D4" s="239"/>
@@ -42235,12 +42232,12 @@
         <v>21</v>
       </c>
       <c r="N6" s="209" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B7" s="11">
         <v>1</v>
@@ -42285,7 +42282,7 @@
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B8" s="65">
         <v>2</v>
@@ -42330,7 +42327,7 @@
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9" s="65">
         <v>3</v>
@@ -42375,7 +42372,7 @@
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10" s="206">
         <v>4</v>
@@ -42420,7 +42417,7 @@
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B11" s="206">
         <v>5</v>
@@ -42465,7 +42462,7 @@
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12" s="206">
         <v>6</v>
@@ -42510,7 +42507,7 @@
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B13" s="206">
         <v>7</v>
@@ -42555,7 +42552,7 @@
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B14" s="206">
         <v>8</v>
@@ -42600,7 +42597,7 @@
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B15" s="206">
         <v>9</v>
@@ -42645,7 +42642,7 @@
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="206">
         <v>10</v>
@@ -42690,7 +42687,7 @@
     </row>
     <row r="17" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="206">
         <v>11</v>
@@ -42735,7 +42732,7 @@
     </row>
     <row r="18" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B18" s="206">
         <v>12</v>
@@ -49156,7 +49153,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F1" s="14">
         <v>45162</v>
@@ -49175,7 +49172,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -49186,7 +49183,7 @@
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C4" s="239"/>
       <c r="D4" s="239"/>
@@ -49254,12 +49251,12 @@
         <v>21</v>
       </c>
       <c r="N6" s="209" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B7" s="11">
         <v>1</v>
@@ -49304,7 +49301,7 @@
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B8" s="65">
         <v>2</v>
@@ -49349,7 +49346,7 @@
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9" s="65">
         <v>3</v>
@@ -49394,7 +49391,7 @@
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10" s="206">
         <v>4</v>
@@ -49439,7 +49436,7 @@
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B11" s="206">
         <v>5</v>
@@ -49484,7 +49481,7 @@
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12" s="206">
         <v>6</v>
@@ -49529,7 +49526,7 @@
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B13" s="206">
         <v>7</v>
@@ -49574,7 +49571,7 @@
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B14" s="206">
         <v>8</v>
@@ -49619,7 +49616,7 @@
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B15" s="206">
         <v>9</v>
@@ -49664,7 +49661,7 @@
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="206">
         <v>10</v>
@@ -49709,7 +49706,7 @@
     </row>
     <row r="17" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="206">
         <v>11</v>
@@ -49754,7 +49751,7 @@
     </row>
     <row r="18" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B18" s="206">
         <v>12</v>
@@ -49821,7 +49818,7 @@
         <v>414</v>
       </c>
       <c r="B1" s="127" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -51286,22 +51283,22 @@
         <v>414</v>
       </c>
       <c r="B1" s="127" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="127" t="s">
         <v>425</v>
       </c>
-      <c r="C1" s="127" t="s">
+      <c r="D1" s="127" t="s">
         <v>426</v>
       </c>
-      <c r="D1" s="127" t="s">
-        <v>427</v>
-      </c>
       <c r="E1" s="127" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F1" s="127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G1" s="127" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -55467,45 +55464,45 @@
         <v>7</v>
       </c>
       <c r="B1" s="127" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="127" t="s">
         <v>425</v>
       </c>
-      <c r="C1" s="127" t="s">
+      <c r="D1" s="127" t="s">
         <v>426</v>
       </c>
-      <c r="D1" s="127" t="s">
-        <v>427</v>
-      </c>
       <c r="E1" s="127" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F1" s="127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G1" s="127" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1" s="127" t="s">
+        <v>488</v>
+      </c>
+      <c r="I1" s="127" t="s">
         <v>489</v>
       </c>
-      <c r="I1" s="127" t="s">
+      <c r="J1" s="127" t="s">
         <v>490</v>
       </c>
-      <c r="J1" s="127" t="s">
+      <c r="K1" s="127" t="s">
         <v>491</v>
       </c>
-      <c r="K1" s="127" t="s">
+      <c r="L1" s="127" t="s">
         <v>492</v>
       </c>
-      <c r="L1" s="127" t="s">
+      <c r="M1" s="127" t="s">
         <v>493</v>
-      </c>
-      <c r="M1" s="127" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="127" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B2" s="198">
         <v>45050</v>
@@ -55546,7 +55543,7 @@
     </row>
     <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="127" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B3" s="198">
         <v>45049</v>
@@ -55587,7 +55584,7 @@
     </row>
     <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="127" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B4" s="198">
         <v>45048</v>
@@ -55628,7 +55625,7 @@
     </row>
     <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="127" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B5" s="198">
         <v>45050</v>
@@ -55669,7 +55666,7 @@
     </row>
     <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="127" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B6" s="198">
         <v>45049</v>
@@ -55710,7 +55707,7 @@
     </row>
     <row r="7" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="127" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7" s="198">
         <v>45050</v>
@@ -55751,7 +55748,7 @@
     </row>
     <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="127" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B8" s="198">
         <v>45050</v>
@@ -55792,7 +55789,7 @@
     </row>
     <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="127" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B9" s="198">
         <v>45049</v>
@@ -55833,7 +55830,7 @@
     </row>
     <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="127" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B10" s="198">
         <v>45050</v>
@@ -55874,7 +55871,7 @@
     </row>
     <row r="11" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="127" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B11" s="198">
         <v>45051</v>
@@ -55915,7 +55912,7 @@
     </row>
     <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="127" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B12" s="198">
         <v>45049</v>
@@ -55956,7 +55953,7 @@
     </row>
     <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="127" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B13" s="198">
         <v>45050</v>
